--- a/sandbox/results/all_metrics_with_outliers_highlighted.xlsx
+++ b/sandbox/results/all_metrics_with_outliers_highlighted.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hallerdi\Documents\Dillon_Classes\geodiversity_2025\sandbox\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kyla Dahlin\Documents\GitHub\geodiversity_2025\sandbox\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{03E00B36-DCC3-4BC6-A6CD-81DF3F99A53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F805990-278E-466B-8F6E-1EE098FAAF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{855828C5-6364-4546-8C58-E286A8F33250}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{855828C5-6364-4546-8C58-E286A8F33250}"/>
   </bookViews>
   <sheets>
     <sheet name="all_metrics_transposed" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>sa_1</t>
   </si>
@@ -267,6 +267,36 @@
   </si>
   <si>
     <t>WOOD_2019_DEM_mosaic_2025-10-22_9.tif</t>
+  </si>
+  <si>
+    <t>human mods?</t>
+  </si>
+  <si>
+    <t>File name</t>
+  </si>
+  <si>
+    <t>minor</t>
+  </si>
+  <si>
+    <t>buildings</t>
+  </si>
+  <si>
+    <t>very minor</t>
+  </si>
+  <si>
+    <t>minor buildings</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>other notes</t>
+  </si>
+  <si>
+    <t>legit cliffs/rocks</t>
+  </si>
+  <si>
+    <t>big lake in middle</t>
   </si>
 </sst>
 </file>
@@ -798,14 +828,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1148,5297 +1171,5422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6AC1FDA-310F-4E80-BFBD-3FDF43FE9C78}">
-  <dimension ref="A1:AU37"/>
+  <dimension ref="A1:AW37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="1" max="1" width="39.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2">
         <v>16.4259437820389</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>20.030080846191701</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>323.56900024414102</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>0.223779227885823</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>231572.317632872</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>2.9387701772667999E-4</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>6.4810944947315999E-2</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>-139.95268839465399</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>0.29436929937399098</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>-0.54969990360466103</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>1.2784781585390001E-2</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>2.0000001992463798</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>10.1010101010101</v>
       </c>
-      <c r="O2">
+      <c r="Q2">
         <v>5.6918657088800603E-2</v>
       </c>
-      <c r="P2">
+      <c r="R2">
         <v>101.010101010101</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>90</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>2.54050322522093E-2</v>
       </c>
-      <c r="S2">
+      <c r="U2">
         <v>-44.905162700555003</v>
       </c>
-      <c r="T2">
+      <c r="V2">
         <v>0.73086553536326304</v>
       </c>
-      <c r="U2">
+      <c r="W2">
         <v>0.55793290974369603</v>
       </c>
-      <c r="V2">
+      <c r="X2">
         <v>-1.2693585155385901E-3</v>
       </c>
-      <c r="W2">
+      <c r="Y2">
         <v>233.25500488281199</v>
       </c>
-      <c r="X2">
+      <c r="Z2">
         <v>325.55700683593801</v>
       </c>
-      <c r="Y2">
+      <c r="AA2">
         <v>56.204060343486297</v>
       </c>
-      <c r="Z2">
+      <c r="AB2">
         <v>272.95014805259802</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>25.485886183105499</v>
       </c>
-      <c r="AB2">
+      <c r="AD2">
         <v>10.6129206778909</v>
       </c>
-      <c r="AC2">
+      <c r="AE2">
         <v>1033.08325195312</v>
       </c>
-      <c r="AD2">
+      <c r="AF2">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE2">
+      <c r="AG2">
         <v>16.5030212402344</v>
       </c>
-      <c r="AF2">
+      <c r="AH2">
         <v>4.7321141892286002E-4</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AI2" s="1">
         <v>1.7118880642684601E-6</v>
       </c>
-      <c r="AH2">
+      <c r="AJ2">
         <v>0.47678304046779602</v>
       </c>
-      <c r="AI2">
+      <c r="AK2">
         <v>1.2062754925550501E-3</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>0.980668993376</v>
       </c>
-      <c r="AK2">
+      <c r="AM2">
         <v>3.2174073514147601</v>
       </c>
-      <c r="AL2">
+      <c r="AN2">
         <v>3.8969187308800501E-2</v>
       </c>
-      <c r="AM2">
+      <c r="AO2">
         <v>4.3052657605963898E-2</v>
       </c>
-      <c r="AN2">
+      <c r="AP2">
         <v>9.8879892404993601</v>
       </c>
-      <c r="AO2">
+      <c r="AQ2">
         <v>-0.16260011113910999</v>
       </c>
-      <c r="AP2">
+      <c r="AR2">
         <v>4.0158092515757297E-2</v>
       </c>
-      <c r="AQ2" s="1">
+      <c r="AS2" s="1">
         <v>1.9258740723010499E-6</v>
       </c>
-      <c r="AR2">
+      <c r="AT2">
         <v>0.144805623465214</v>
       </c>
-      <c r="AS2">
+      <c r="AU2">
         <v>0.476965915054062</v>
       </c>
-      <c r="AT2">
+      <c r="AV2">
         <v>0.168632916464792</v>
       </c>
-      <c r="AU2">
+      <c r="AW2">
         <v>0.480511457159637</v>
       </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3">
         <v>18.739303066998001</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>23.0164758713568</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>336.841796875</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>0.29514330819137702</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>230759.72088779099</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>3.9372018150740998E-4</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>7.3242329707130294E-2</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>-132.66099173969701</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>0.48251722136499298</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>-0.51010202640673197</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>1.51431393535687E-2</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>2.0000002973789801</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>10.1010101010101</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>5.5402633483360997E-2</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>80.808080808080803</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>90</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>2.8528296619702201E-2</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>-44.477920708251901</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>0.72636307471013695</v>
       </c>
-      <c r="U3">
+      <c r="W3">
         <v>0.55481544626573698</v>
       </c>
-      <c r="V3">
+      <c r="X3">
         <v>-1.0846135656909001E-3</v>
       </c>
-      <c r="W3">
+      <c r="Y3">
         <v>231.80599975585901</v>
       </c>
-      <c r="X3">
+      <c r="Z3">
         <v>336.98098754882801</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>52.876853424030699</v>
       </c>
-      <c r="Z3">
+      <c r="AB3">
         <v>271.82564514538802</v>
       </c>
-      <c r="AA3">
+      <c r="AC3">
         <v>42.193811313148601</v>
       </c>
-      <c r="AB3">
+      <c r="AD3">
         <v>10.104908417511201</v>
       </c>
-      <c r="AC3">
+      <c r="AE3">
         <v>1026.71899414062</v>
       </c>
-      <c r="AD3">
+      <c r="AF3">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE3">
+      <c r="AG3">
         <v>22.72998046875</v>
       </c>
-      <c r="AF3">
+      <c r="AH3">
         <v>6.9666638041479003E-4</v>
       </c>
-      <c r="AG3" s="1">
+      <c r="AI3" s="1">
         <v>-3.1472061821604601E-6</v>
       </c>
-      <c r="AH3">
+      <c r="AJ3">
         <v>0.58798229450087802</v>
       </c>
-      <c r="AI3">
+      <c r="AK3">
         <v>1.65279860041871E-3</v>
       </c>
-      <c r="AJ3">
+      <c r="AL3">
         <v>0.967232455928413</v>
       </c>
-      <c r="AK3">
+      <c r="AM3">
         <v>3.2174069320416301</v>
       </c>
-      <c r="AL3">
+      <c r="AN3">
         <v>4.2418313045388699E-2</v>
       </c>
-      <c r="AM3">
+      <c r="AO3">
         <v>4.6426898064435902E-2</v>
       </c>
-      <c r="AN3">
+      <c r="AP3">
         <v>12.043655293967401</v>
       </c>
-      <c r="AO3">
+      <c r="AQ3">
         <v>3.1988164286513202E-2</v>
       </c>
-      <c r="AP3">
+      <c r="AR3">
         <v>2.1633019137894199E-2</v>
       </c>
-      <c r="AQ3" s="1">
+      <c r="AS3" s="1">
         <v>-3.5406069549190901E-6</v>
       </c>
-      <c r="AR3">
+      <c r="AT3">
         <v>0.17993312296212399</v>
       </c>
-      <c r="AS3">
+      <c r="AU3">
         <v>0.58837735832900395</v>
       </c>
-      <c r="AT3">
+      <c r="AV3">
         <v>0.20802280998554201</v>
       </c>
-      <c r="AU3">
+      <c r="AW3">
         <v>0.58744130845074005</v>
       </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4">
         <v>19.464191355990899</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>24.450263136870799</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>357.79260253906199</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>0.29961461664633798</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>227225.05212479801</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>2.602535423725E-4</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>7.7212736356662606E-2</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>-120.8683578823</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>1.1123024165523701</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>0.74267393142959304</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>1.2272269201133799E-2</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>2.0000001488065</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>10.1010101010101</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>5.3192264758435602E-2</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>80.808080808080803</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>90</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>2.9555583115041101E-2</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>-44.120704731790397</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>0.732276224613855</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>0.55701986951707405</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>-8.7817581258238997E-4</v>
       </c>
-      <c r="W4">
+      <c r="Y4">
         <v>226.55999755859401</v>
       </c>
-      <c r="X4">
+      <c r="Z4">
         <v>357.88900756835898</v>
       </c>
-      <c r="Y4">
+      <c r="AA4">
         <v>42.2131179209794</v>
       </c>
-      <c r="Z4">
+      <c r="AB4">
         <v>267.45088280894902</v>
       </c>
-      <c r="AA4">
+      <c r="AC4">
         <v>76.740755602294897</v>
       </c>
-      <c r="AB4">
+      <c r="AD4">
         <v>12.3759673751909</v>
       </c>
-      <c r="AC4">
+      <c r="AE4">
         <v>1035.07727050781</v>
       </c>
-      <c r="AD4">
+      <c r="AF4">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE4">
+      <c r="AG4">
         <v>41.227996826171903</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>5.0964545711362004E-4</v>
       </c>
-      <c r="AG4" s="1">
+      <c r="AI4" s="1">
         <v>2.5496502107857301E-5</v>
       </c>
-      <c r="AH4">
+      <c r="AJ4">
         <v>0.60997650846523799</v>
       </c>
-      <c r="AI4">
+      <c r="AK4">
         <v>1.5797354333516899E-3</v>
       </c>
-      <c r="AJ4">
+      <c r="AL4">
         <v>0.96538443487801395</v>
       </c>
-      <c r="AK4">
+      <c r="AM4">
         <v>3.2174068918469501</v>
       </c>
-      <c r="AL4">
+      <c r="AN4">
         <v>4.05770331922614E-2</v>
       </c>
-      <c r="AM4">
+      <c r="AO4">
         <v>4.4295472142897703E-2</v>
       </c>
-      <c r="AN4">
+      <c r="AP4">
         <v>12.6495249321394</v>
       </c>
-      <c r="AO4">
+      <c r="AQ4">
         <v>-0.10711850396980301</v>
       </c>
-      <c r="AP4">
+      <c r="AR4">
         <v>-0.11221740559070199</v>
       </c>
-      <c r="AQ4" s="1">
+      <c r="AS4" s="1">
         <v>2.8683564871348701E-5</v>
       </c>
-      <c r="AR4">
+      <c r="AT4">
         <v>0.187126854417101</v>
       </c>
-      <c r="AS4">
+      <c r="AU4">
         <v>0.61024999208836594</v>
       </c>
-      <c r="AT4">
+      <c r="AV4">
         <v>0.215755953812377</v>
       </c>
-      <c r="AU4">
+      <c r="AW4">
         <v>0.61284540119153996</v>
       </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5">
         <v>14.7878675285101</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>18.093016373227002</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>324.94499511718698</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>0.27999647259222099</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>222452.94217930199</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>4.1089013090462998E-4</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>6.09143273819516E-2</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>-136.357263553038</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>0.70257261192681497</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>-0.34492161201614402</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>1.3543039653893999E-2</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>2.0000003480041801</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>10.1010101010101</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>5.3230000971511197E-2</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>70.707070707070699</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>3.0492316408429102E-2</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>-44.273742034195998</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>0.71035509816272702</v>
       </c>
-      <c r="U5">
+      <c r="W5">
         <v>0.54379967746297997</v>
       </c>
-      <c r="V5">
+      <c r="X5">
         <v>-1.18324288494714E-3</v>
       </c>
-      <c r="W5">
+      <c r="Y5">
         <v>227.31799316406199</v>
       </c>
-      <c r="X5">
+      <c r="Z5">
         <v>324.99200439453102</v>
       </c>
-      <c r="Y5">
+      <c r="AA5">
         <v>36.452291920255099</v>
       </c>
-      <c r="Z5">
+      <c r="AB5">
         <v>262.27079183437002</v>
       </c>
-      <c r="AA5">
+      <c r="AC5">
         <v>49.022774826530501</v>
       </c>
-      <c r="AB5">
+      <c r="AD5">
         <v>12.199956205322099</v>
       </c>
-      <c r="AC5">
+      <c r="AE5">
         <v>1004.09161376953</v>
       </c>
-      <c r="AD5">
+      <c r="AF5">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE5">
+      <c r="AG5">
         <v>27.968017578125</v>
       </c>
-      <c r="AF5">
+      <c r="AH5">
         <v>5.5604141274847999E-4</v>
       </c>
-      <c r="AG5" s="1">
+      <c r="AI5" s="1">
         <v>8.9138054660532905E-6</v>
       </c>
-      <c r="AH5">
+      <c r="AJ5">
         <v>0.54930186183989704</v>
       </c>
-      <c r="AI5">
+      <c r="AK5">
         <v>1.60890173889138E-3</v>
       </c>
-      <c r="AJ5">
+      <c r="AL5">
         <v>0.970730079455565</v>
       </c>
-      <c r="AK5">
+      <c r="AM5">
         <v>3.21740696794576</v>
       </c>
-      <c r="AL5">
+      <c r="AN5">
         <v>3.96013707112782E-2</v>
       </c>
-      <c r="AM5">
+      <c r="AO5">
         <v>4.2845110812371003E-2</v>
       </c>
-      <c r="AN5">
+      <c r="AP5">
         <v>11.3142563106364</v>
       </c>
-      <c r="AO5">
+      <c r="AQ5">
         <v>-0.121019109956048</v>
       </c>
-      <c r="AP5">
+      <c r="AR5">
         <v>3.9125584308886199E-2</v>
       </c>
-      <c r="AQ5" s="1">
+      <c r="AS5" s="1">
         <v>1.0028031149318799E-5</v>
       </c>
-      <c r="AR5">
+      <c r="AT5">
         <v>0.167703510360034</v>
       </c>
-      <c r="AS5">
+      <c r="AU5">
         <v>0.54964747274144599</v>
       </c>
-      <c r="AT5">
+      <c r="AV5">
         <v>0.19432972761873199</v>
       </c>
-      <c r="AU5">
+      <c r="AW5">
         <v>0.55099860895428499</v>
       </c>
     </row>
-    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6">
         <v>23.073191267478698</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>27.198378787456601</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>362.69559936523399</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>0.26743909480459699</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>246288.64417003101</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>2.4702493596828002E-4</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>8.1880160180454103E-2</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>-140.23618983444001</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>0.119645205857572</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>-0.949335064313097</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>1.1503500624749601E-2</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>2.0000002116340601</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>10.1010101010101</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>6.1858132443541797E-2</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>111.111111111111</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>2.12551694943992E-2</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>-46.948633972387697</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>0.69440550091947395</v>
       </c>
-      <c r="U6">
+      <c r="W6">
         <v>0.53135508382698105</v>
       </c>
-      <c r="V6">
+      <c r="X6">
         <v>-9.9738690167684003E-4</v>
       </c>
-      <c r="W6">
+      <c r="Y6">
         <v>242.47000122070301</v>
       </c>
-      <c r="X6">
+      <c r="Z6">
         <v>362.7919921875</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <v>83.324344283612902</v>
       </c>
-      <c r="Z6">
+      <c r="AB6">
         <v>289.77506757987697</v>
       </c>
-      <c r="AA6">
+      <c r="AC6">
         <v>30.728952805496199</v>
       </c>
-      <c r="AB6">
+      <c r="AD6">
         <v>6.2699641753155202</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <v>981.54675292968795</v>
       </c>
-      <c r="AD6">
+      <c r="AF6">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE6">
+      <c r="AG6">
         <v>30.6189880371094</v>
       </c>
-      <c r="AF6">
+      <c r="AH6">
         <v>3.8441814202712002E-4</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AI6" s="1">
         <v>3.0306237228028299E-5</v>
       </c>
-      <c r="AH6">
+      <c r="AJ6">
         <v>0.55828618622211501</v>
       </c>
-      <c r="AI6">
+      <c r="AK6">
         <v>1.57339335426932E-3</v>
       </c>
-      <c r="AJ6">
+      <c r="AL6">
         <v>0.97253730684638395</v>
       </c>
-      <c r="AK6">
+      <c r="AM6">
         <v>3.2174071845198502</v>
       </c>
-      <c r="AL6">
+      <c r="AN6">
         <v>4.1689541439674897E-2</v>
       </c>
-      <c r="AM6">
+      <c r="AO6">
         <v>4.55823261061295E-2</v>
       </c>
-      <c r="AN6">
+      <c r="AP6">
         <v>11.6351616721808</v>
       </c>
-      <c r="AO6">
+      <c r="AQ6">
         <v>-5.4990407704456297E-2</v>
       </c>
-      <c r="AP6">
+      <c r="AR6">
         <v>4.2304799246584502E-3</v>
       </c>
-      <c r="AQ6" s="1">
+      <c r="AS6" s="1">
         <v>3.4094516881537499E-5</v>
       </c>
-      <c r="AR6">
+      <c r="AT6">
         <v>0.17022986996632</v>
       </c>
-      <c r="AS6">
+      <c r="AU6">
         <v>0.55866477631928702</v>
       </c>
-      <c r="AT6">
+      <c r="AV6">
         <v>0.19751782587271599</v>
       </c>
-      <c r="AU6">
+      <c r="AW6">
         <v>0.562842096459924</v>
       </c>
     </row>
-    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7">
         <v>16.941759844098801</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>20.736214655244201</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>354.90960083007798</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>0.33593229157075699</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>243560.46710197799</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>5.0472116318979997E-4</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>6.3451339850907104E-2</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>-147.847311687071</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>0.62763473306290396</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>-0.22068647214413301</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>8.7137115331052204E-3</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>2.0000005335893598</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>10.1010101010101</v>
       </c>
-      <c r="O7">
+      <c r="Q7">
         <v>5.1530782189157603E-2</v>
       </c>
-      <c r="P7">
+      <c r="R7">
         <v>60.606060606060602</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>3.44441923590387E-2</v>
       </c>
-      <c r="S7">
+      <c r="U7">
         <v>-48.4755038700944</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>0.71142596113838297</v>
       </c>
-      <c r="U7">
+      <c r="W7">
         <v>0.54450744016596297</v>
       </c>
-      <c r="V7">
+      <c r="X7">
         <v>-1.1007169065121801E-3</v>
       </c>
-      <c r="W7">
+      <c r="Y7">
         <v>249.225997924805</v>
       </c>
-      <c r="X7">
+      <c r="Z7">
         <v>354.95401000976602</v>
       </c>
-      <c r="Y7">
+      <c r="AA7">
         <v>52.015699536640099</v>
       </c>
-      <c r="Z7">
+      <c r="AB7">
         <v>287.11115510086597</v>
       </c>
-      <c r="AA7">
+      <c r="AC7">
         <v>45.210847302978401</v>
       </c>
-      <c r="AB7">
+      <c r="AD7">
         <v>8.5019595816878599</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <v>1005.60528564453</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE7">
+      <c r="AG7">
         <v>28.1490173339844</v>
       </c>
-      <c r="AF7">
+      <c r="AH7">
         <v>5.0424487800003004E-4</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AI7" s="1">
         <v>-8.6155564919726708E-6</v>
       </c>
-      <c r="AH7">
+      <c r="AJ7">
         <v>0.70091390118873198</v>
       </c>
-      <c r="AI7">
+      <c r="AK7">
         <v>1.6580479343867699E-3</v>
       </c>
-      <c r="AJ7">
+      <c r="AL7">
         <v>0.95587204080146004</v>
       </c>
-      <c r="AK7">
+      <c r="AM7">
         <v>3.2174067405292801</v>
       </c>
-      <c r="AL7">
+      <c r="AN7">
         <v>4.1075017680922699E-2</v>
       </c>
-      <c r="AM7">
+      <c r="AO7">
         <v>4.4472292218480598E-2</v>
       </c>
-      <c r="AN7">
+      <c r="AP7">
         <v>14.7142280392122</v>
       </c>
-      <c r="AO7">
+      <c r="AQ7">
         <v>-0.107875074518496</v>
       </c>
-      <c r="AP7">
+      <c r="AR7">
         <v>-2.67352949677899E-2</v>
       </c>
-      <c r="AQ7" s="1">
+      <c r="AS7" s="1">
         <v>-9.6925010534718603E-6</v>
       </c>
-      <c r="AR7">
+      <c r="AT7">
         <v>0.215758971307771</v>
       </c>
-      <c r="AS7">
+      <c r="AU7">
         <v>0.70133709770915398</v>
       </c>
-      <c r="AT7">
+      <c r="AV7">
         <v>0.247960108843917</v>
       </c>
-      <c r="AU7">
+      <c r="AW7">
         <v>0.71179087287693898</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8">
         <v>33.8015238009922</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>43.912710139475699</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>412.71420288085898</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>0.32405697556824498</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>234662.393595578</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>1.5289629212421999E-4</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>0.11715272994699</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>-70.1960346462091</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>1.4444173307064001</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>0.90493913404778803</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>1.0702700024349299E-2</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>2.0000000791991299</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>10.1010101010101</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>6.68095415741497E-2</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>111.111111111111</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>2.3888990302187201E-2</v>
       </c>
-      <c r="S8">
+      <c r="U8">
         <v>-44.178149704365197</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>0.74458216740248195</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>0.55840322585380997</v>
       </c>
-      <c r="V8">
+      <c r="X8">
         <v>-6.0354720612295005E-4</v>
       </c>
-      <c r="W8">
+      <c r="Y8">
         <v>227.49000549316401</v>
       </c>
-      <c r="X8">
+      <c r="Z8">
         <v>412.80300903320301</v>
       </c>
-      <c r="Y8">
+      <c r="AA8">
         <v>46.203909440104098</v>
       </c>
-      <c r="Z8">
+      <c r="AB8">
         <v>274.029366571803</v>
       </c>
-      <c r="AA8">
+      <c r="AC8">
         <v>132.88575502829701</v>
       </c>
-      <c r="AB8">
+      <c r="AD8">
         <v>6.2239475258942303</v>
       </c>
-      <c r="AC8">
+      <c r="AE8">
         <v>1052.47180175781</v>
       </c>
-      <c r="AD8">
+      <c r="AF8">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE8">
+      <c r="AG8">
         <v>37.970001220703097</v>
       </c>
-      <c r="AF8">
+      <c r="AH8">
         <v>4.8663187479406998E-4</v>
       </c>
-      <c r="AG8" s="1">
+      <c r="AI8" s="1">
         <v>1.49739131753846E-5</v>
       </c>
-      <c r="AH8">
+      <c r="AJ8">
         <v>0.64731551533013598</v>
       </c>
-      <c r="AI8">
+      <c r="AK8">
         <v>1.92328621560782E-3</v>
       </c>
-      <c r="AJ8">
+      <c r="AL8">
         <v>0.96066382195498901</v>
       </c>
-      <c r="AK8">
+      <c r="AM8">
         <v>3.2174067243197202</v>
       </c>
-      <c r="AL8">
+      <c r="AN8">
         <v>4.16217135483547E-2</v>
       </c>
-      <c r="AM8">
+      <c r="AO8">
         <v>4.4807173393233403E-2</v>
       </c>
-      <c r="AN8">
+      <c r="AP8">
         <v>13.4395939961938</v>
       </c>
-      <c r="AO8">
+      <c r="AQ8">
         <v>-3.3636243633627702E-2</v>
       </c>
-      <c r="AP8">
+      <c r="AR8">
         <v>-7.3766274644497198E-2</v>
       </c>
-      <c r="AQ8" s="1">
+      <c r="AS8" s="1">
         <v>1.6845652322304099E-5</v>
       </c>
-      <c r="AR8">
+      <c r="AT8">
         <v>0.19852721628504999</v>
       </c>
-      <c r="AS8">
+      <c r="AU8">
         <v>0.64759677822440198</v>
       </c>
-      <c r="AT8">
+      <c r="AV8">
         <v>0.228960036678545</v>
       </c>
-      <c r="AU8">
+      <c r="AW8">
         <v>0.64934524852255504</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9">
         <v>20.1026174078923</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>23.745999699647399</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>340.75739135742202</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>0.35435855445699599</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>234842.04658123199</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>5.7432210863341004E-4</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>7.3940062973105805E-2</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>-133.30405530455801</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>0.57434213326026595</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>-0.52712245350989495</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>1.27905373397054E-2</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>2.00000029910092</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>10.1010101010101</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>6.8350304388389099E-2</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>111.111111111111</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>2.4523206298038398E-2</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>-45.8803271290015</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>0.73436708457382205</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>0.55485875576430899</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>-1.2396367292327899E-3</v>
       </c>
-      <c r="W9">
+      <c r="Y9">
         <v>236.33399963378901</v>
       </c>
-      <c r="X9">
+      <c r="Z9">
         <v>340.87899780273398</v>
       </c>
-      <c r="Y9">
+      <c r="AA9">
         <v>52.924059752857303</v>
       </c>
-      <c r="Z9">
+      <c r="AB9">
         <v>276.57447966063802</v>
       </c>
-      <c r="AA9">
+      <c r="AC9">
         <v>43.961778735702502</v>
       </c>
-      <c r="AB9">
+      <c r="AD9">
         <v>7.6599657823029501</v>
       </c>
-      <c r="AC9">
+      <c r="AE9">
         <v>1038.03271484375</v>
       </c>
-      <c r="AD9">
+      <c r="AF9">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE9">
+      <c r="AG9">
         <v>19.7269897460938</v>
       </c>
-      <c r="AF9">
+      <c r="AH9">
         <v>7.1514668995033997E-4</v>
       </c>
-      <c r="AG9" s="1">
+      <c r="AI9" s="1">
         <v>-4.9515837865866698E-6</v>
       </c>
-      <c r="AH9">
+      <c r="AJ9">
         <v>0.55673642636227205</v>
       </c>
-      <c r="AI9">
+      <c r="AK9">
         <v>2.2699339645131001E-3</v>
       </c>
-      <c r="AJ9">
+      <c r="AL9">
         <v>0.97058141037224399</v>
       </c>
-      <c r="AK9">
+      <c r="AM9">
         <v>3.21740671018267</v>
       </c>
-      <c r="AL9">
+      <c r="AN9">
         <v>4.46855065173958E-2</v>
       </c>
-      <c r="AM9">
+      <c r="AO9">
         <v>4.8357745311104101E-2</v>
       </c>
-      <c r="AN9">
+      <c r="AP9">
         <v>11.0806430510774</v>
       </c>
-      <c r="AO9">
+      <c r="AQ9">
         <v>-0.103068545024423</v>
       </c>
-      <c r="AP9">
+      <c r="AR9">
         <v>2.4743953964595299E-2</v>
       </c>
-      <c r="AQ9" s="1">
+      <c r="AS9" s="1">
         <v>-5.5705317599253496E-6</v>
       </c>
-      <c r="AR9">
+      <c r="AT9">
         <v>0.16782512630881199</v>
       </c>
-      <c r="AS9">
+      <c r="AU9">
         <v>0.55695995669482201</v>
       </c>
-      <c r="AT9">
+      <c r="AV9">
         <v>0.19691508111412401</v>
       </c>
-      <c r="AU9">
+      <c r="AW9">
         <v>0.55521478136470204</v>
       </c>
     </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10">
         <v>19.026304168667799</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>22.120614919201898</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>362.79420166015598</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>0.29315534538124999</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>252603.85482532499</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>3.8007418282417002E-4</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>6.6326495455950193E-2</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>-157.66613179061099</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>0.19675976243395801</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>-1.0530606870758401</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>1.13551022634879E-2</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>2.0000002862669302</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>10.1010101010101</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>5.8493772618321803E-2</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>90.909090909090907</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
         <v>2.6875557424526901E-2</v>
       </c>
-      <c r="S10">
+      <c r="U10">
         <v>-49.855396943976203</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>0.71172770268974905</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>0.54360221551186505</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>-1.09734343358455E-3</v>
       </c>
-      <c r="W10">
+      <c r="Y10">
         <v>256.68099975585898</v>
       </c>
-      <c r="X10">
+      <c r="Z10">
         <v>362.99499511718801</v>
       </c>
-      <c r="Y10">
+      <c r="AA10">
         <v>64.853618256097107</v>
       </c>
-      <c r="Z10">
+      <c r="AB10">
         <v>297.77013795421499</v>
       </c>
-      <c r="AA10">
+      <c r="AC10">
         <v>35.429875581321802</v>
       </c>
-      <c r="AB10">
+      <c r="AD10">
         <v>6.0309811385803904</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>1006.03179931641</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>29.4840087890625</v>
       </c>
-      <c r="AF10">
+      <c r="AH10">
         <v>5.1545696139907999E-4</v>
       </c>
-      <c r="AG10" s="1">
+      <c r="AI10" s="1">
         <v>1.02803355130337E-5</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>0.55802055939848005</v>
       </c>
-      <c r="AI10">
+      <c r="AK10">
         <v>1.55216586502624E-3</v>
       </c>
-      <c r="AJ10">
+      <c r="AL10">
         <v>0.97091196354660303</v>
       </c>
-      <c r="AK10">
+      <c r="AM10">
         <v>3.2174071296409501</v>
       </c>
-      <c r="AL10">
+      <c r="AN10">
         <v>3.8652757239117701E-2</v>
       </c>
-      <c r="AM10">
+      <c r="AO10">
         <v>4.2152748819538698E-2</v>
       </c>
-      <c r="AN10">
+      <c r="AP10">
         <v>11.5772818831514</v>
       </c>
-      <c r="AO10">
+      <c r="AQ10">
         <v>-7.7970089482572794E-2</v>
       </c>
-      <c r="AP10">
+      <c r="AR10">
         <v>-3.6237802536459703E-2</v>
       </c>
-      <c r="AQ10" s="1">
+      <c r="AS10" s="1">
         <v>1.15653774521611E-5</v>
       </c>
-      <c r="AR10">
+      <c r="AT10">
         <v>0.17006394137268999</v>
       </c>
-      <c r="AS10">
+      <c r="AU10">
         <v>0.55824589036054495</v>
       </c>
-      <c r="AT10">
+      <c r="AV10">
         <v>0.19736972732171701</v>
       </c>
-      <c r="AU10">
+      <c r="AW10">
         <v>0.56605905660126499</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11">
         <v>42.558964302041197</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>51.778582470464897</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>2850.3100097656302</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>0.261410502717844</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>2266174.8111370802</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>3.2392166535158403E-5</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>1.8734358121462999E-2</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>-1852.1942766079601</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>0.64935347145553202</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>0.24254850395142299</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>1.70067525008127E-2</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>2.0000000160721001</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>10.1010101010101</v>
       </c>
-      <c r="O11">
+      <c r="Q11">
         <v>8.9003288915187495E-2</v>
       </c>
-      <c r="P11">
+      <c r="R11">
         <v>161.616161616162</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>90</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>3.7999129415846003E-2</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>-512.30975195312499</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>0.72936459999899805</v>
       </c>
-      <c r="U11">
+      <c r="W11">
         <v>0.55777905955086304</v>
       </c>
-      <c r="V11">
+      <c r="X11">
         <v>-4.7211969857741001E-4</v>
       </c>
-      <c r="W11">
+      <c r="Y11">
         <v>2584.32006835938</v>
       </c>
-      <c r="X11">
+      <c r="Z11">
         <v>2909.080078125</v>
       </c>
-      <c r="Y11">
+      <c r="AA11">
         <v>129.27681941568301</v>
       </c>
-      <c r="Z11">
+      <c r="AB11">
         <v>2678.2021620953001</v>
       </c>
-      <c r="AA11">
+      <c r="AC11">
         <v>174.91860431201101</v>
       </c>
-      <c r="AB11">
+      <c r="AD11">
         <v>20.569372558106402</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <v>1030.96166992188</v>
       </c>
-      <c r="AD11">
+      <c r="AF11">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE11">
+      <c r="AG11">
         <v>145.25</v>
       </c>
-      <c r="AF11">
+      <c r="AH11">
         <v>1.5084314668903499E-3</v>
       </c>
-      <c r="AG11" s="1">
+      <c r="AI11" s="1">
         <v>-4.6033943511097597E-5</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11">
         <v>0.50705843341455503</v>
       </c>
-      <c r="AI11">
+      <c r="AK11">
         <v>1.9771439420423901E-3</v>
       </c>
-      <c r="AJ11">
+      <c r="AL11">
         <v>0.97717426288529297</v>
       </c>
-      <c r="AK11">
+      <c r="AM11">
         <v>3.21740787945622</v>
       </c>
-      <c r="AL11">
+      <c r="AN11">
         <v>4.7382880982507598E-2</v>
       </c>
-      <c r="AM11">
+      <c r="AO11">
         <v>5.2514631722642001E-2</v>
       </c>
-      <c r="AN11">
+      <c r="AP11">
         <v>10.097793494192199</v>
       </c>
-      <c r="AO11">
+      <c r="AQ11">
         <v>-4.1435428583253602E-2</v>
       </c>
-      <c r="AP11">
+      <c r="AR11">
         <v>0.52447896821200202</v>
       </c>
-      <c r="AQ11" s="1">
+      <c r="AS11" s="1">
         <v>-5.17881864499478E-5</v>
       </c>
-      <c r="AR11">
+      <c r="AT11">
         <v>0.15310421155363699</v>
       </c>
-      <c r="AS11">
+      <c r="AU11">
         <v>0.50715762879669102</v>
       </c>
-      <c r="AT11">
+      <c r="AV11">
         <v>0.17930729922630501</v>
       </c>
-      <c r="AU11">
+      <c r="AW11">
         <v>0.50082895334237998</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>56</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12">
         <v>40.0573893220608</v>
       </c>
-      <c r="C12">
+      <c r="E12">
         <v>47.747727532145099</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>2843.35</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>0.25466726246336002</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>2300477.05758717</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>6.4369123956758005E-5</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>1.7036271393624201E-2</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>-1882.1130305744</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>0.27052084957202299</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>-0.81765560124811199</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>1.8574569926283799E-2</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>2.0000000246948502</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>10.1010101010101</v>
       </c>
-      <c r="O12">
+      <c r="Q12">
         <v>7.3144844020393396E-2</v>
       </c>
-      <c r="P12">
+      <c r="R12">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>90</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>3.1059152980112501E-2</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>-519.05223804958302</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>0.72786401007440205</v>
       </c>
-      <c r="U12">
+      <c r="W12">
         <v>0.55699426380156702</v>
       </c>
-      <c r="V12">
+      <c r="X12">
         <v>-6.8778680864139995E-4</v>
       </c>
-      <c r="W12">
+      <c r="Y12">
         <v>2619.89990234375</v>
       </c>
-      <c r="X12">
+      <c r="Z12">
         <v>2844.35009765625</v>
       </c>
-      <c r="Y12">
+      <c r="AA12">
         <v>130.14120794672101</v>
       </c>
-      <c r="Z12">
+      <c r="AB12">
         <v>2718.79000950727</v>
       </c>
-      <c r="AA12">
+      <c r="AC12">
         <v>65.908786015685607</v>
       </c>
-      <c r="AB12">
+      <c r="AD12">
         <v>28.399662474667799</v>
       </c>
-      <c r="AC12">
+      <c r="AE12">
         <v>1028.84057617188</v>
       </c>
-      <c r="AD12">
+      <c r="AF12">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE12">
+      <c r="AG12">
         <v>41.64013671875</v>
       </c>
-      <c r="AF12">
+      <c r="AH12">
         <v>7.3700779783067005E-4</v>
       </c>
-      <c r="AG12" s="1">
+      <c r="AI12" s="1">
         <v>-1.8443056634968501E-5</v>
       </c>
-      <c r="AH12">
+      <c r="AJ12">
         <v>0.49164090290471701</v>
       </c>
-      <c r="AI12">
+      <c r="AK12">
         <v>2.29091127724708E-3</v>
       </c>
-      <c r="AJ12">
+      <c r="AL12">
         <v>0.97903876615293695</v>
       </c>
-      <c r="AK12">
+      <c r="AM12">
         <v>3.2173764963442699</v>
       </c>
-      <c r="AL12">
+      <c r="AN12">
         <v>4.97336771344477E-2</v>
       </c>
-      <c r="AM12">
+      <c r="AO12">
         <v>5.5162685606450802E-2</v>
       </c>
-      <c r="AN12">
+      <c r="AP12">
         <v>9.6004166905156705</v>
       </c>
-      <c r="AO12">
+      <c r="AQ12">
         <v>-0.144598016191887</v>
       </c>
-      <c r="AP12">
+      <c r="AR12">
         <v>0.46853858193637699</v>
       </c>
-      <c r="AQ12" s="1">
+      <c r="AS12" s="1">
         <v>-2.0748438714439399E-5</v>
       </c>
-      <c r="AR12">
+      <c r="AT12">
         <v>0.14785606713923399</v>
       </c>
-      <c r="AS12">
+      <c r="AU12">
         <v>0.49174498008234502</v>
       </c>
-      <c r="AT12">
+      <c r="AV12">
         <v>0.173858105015325</v>
       </c>
-      <c r="AU12">
+      <c r="AW12">
         <v>0.47992936928772201</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13">
         <v>50.197473528450701</v>
       </c>
-      <c r="C13">
+      <c r="E13">
         <v>65.815773376359004</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>3007.96997070312</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>0.32122777514523099</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>2352086.8780385102</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>4.4619357532752103E-5</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>2.2442958631308501E-2</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>-1855.56031711527</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>1.3651831507810701</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>1.29925646605816</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>1.3575822428472901E-2</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>2.0000000117049401</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>10.1010101010101</v>
       </c>
-      <c r="O13">
+      <c r="Q13">
         <v>8.6727729811294896E-2</v>
       </c>
-      <c r="P13">
+      <c r="R13">
         <v>151.51515151515201</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>90</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>2.5551152127024301E-2</v>
       </c>
-      <c r="S13">
+      <c r="U13">
         <v>-531.97741421697901</v>
       </c>
-      <c r="T13">
+      <c r="V13">
         <v>0.73089429321575505</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>0.55815580469048298</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>-4.4403062305803999E-4</v>
       </c>
-      <c r="W13">
+      <c r="Y13">
         <v>2679.15991210938</v>
       </c>
-      <c r="X13">
+      <c r="Z13">
         <v>3019.18994140625</v>
       </c>
-      <c r="Y13">
+      <c r="AA13">
         <v>97.812043899143603</v>
       </c>
-      <c r="Z13">
+      <c r="AB13">
         <v>2779.7661295192102</v>
       </c>
-      <c r="AA13">
+      <c r="AC13">
         <v>212.25761972387701</v>
       </c>
-      <c r="AB13">
+      <c r="AD13">
         <v>29.959774207762202</v>
       </c>
-      <c r="AC13">
+      <c r="AE13">
         <v>1033.12390136719</v>
       </c>
-      <c r="AD13">
+      <c r="AF13">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE13">
+      <c r="AG13">
         <v>86.60986328125</v>
       </c>
-      <c r="AF13">
+      <c r="AH13">
         <v>2.9552228997958E-4</v>
       </c>
-      <c r="AG13" s="1">
+      <c r="AI13" s="1">
         <v>-6.09787011654859E-5</v>
       </c>
-      <c r="AH13">
+      <c r="AJ13">
         <v>0.59916156957732802</v>
       </c>
-      <c r="AI13">
+      <c r="AK13">
         <v>2.4488036924552202E-3</v>
       </c>
-      <c r="AJ13">
+      <c r="AL13">
         <v>0.96708259494382998</v>
       </c>
-      <c r="AK13">
+      <c r="AM13">
         <v>3.21740787639472</v>
       </c>
-      <c r="AL13">
+      <c r="AN13">
         <v>5.0222328496746897E-2</v>
       </c>
-      <c r="AM13">
+      <c r="AO13">
         <v>5.5606433799100401E-2</v>
       </c>
-      <c r="AN13">
+      <c r="AP13">
         <v>11.956439242228701</v>
       </c>
-      <c r="AO13">
+      <c r="AQ13">
         <v>-0.16456263881232899</v>
       </c>
-      <c r="AP13">
+      <c r="AR13">
         <v>7.09493096036786E-3</v>
       </c>
-      <c r="AQ13" s="1">
+      <c r="AS13" s="1">
         <v>-6.8601038811056002E-5</v>
       </c>
-      <c r="AR13">
+      <c r="AT13">
         <v>0.18210433707854801</v>
       </c>
-      <c r="AS13">
+      <c r="AU13">
         <v>0.599387250476481</v>
       </c>
-      <c r="AT13">
+      <c r="AV13">
         <v>0.21191539468441001</v>
       </c>
-      <c r="AU13">
+      <c r="AW13">
         <v>0.58811003632051495</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>58</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14">
         <v>30.4223645352196</v>
       </c>
-      <c r="C14">
+      <c r="E14">
         <v>37.726004162480102</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>2681.6419921874999</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>0.31357101854969299</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>2182619.5508279498</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>1.3794117500591E-4</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>1.4239129754250301E-2</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>-1803.4976414892001</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>0.23031050907160999</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>-0.48730783511188402</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>1.13811282830009E-2</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>2.00000007369764</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>10.1010101010101</v>
       </c>
-      <c r="O14">
+      <c r="Q14">
         <v>7.3033668024619705E-2</v>
       </c>
-      <c r="P14">
+      <c r="R14">
         <v>141.414141414141</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
         <v>2.3337760168438901E-2</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>-494.436175391966</v>
       </c>
-      <c r="T14">
+      <c r="V14">
         <v>0.73036507964197905</v>
       </c>
-      <c r="U14">
+      <c r="W14">
         <v>0.55785980607362395</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>-8.1147267025990003E-4</v>
       </c>
-      <c r="W14">
+      <c r="Y14">
         <v>2495.89990234375</v>
       </c>
-      <c r="X14">
+      <c r="Z14">
         <v>2684.69995117188</v>
       </c>
-      <c r="Y14">
+      <c r="AA14">
         <v>95.874198589625806</v>
       </c>
-      <c r="Z14">
+      <c r="AB14">
         <v>2579.89681511135</v>
       </c>
-      <c r="AA14">
+      <c r="AC14">
         <v>58.1385744496461</v>
       </c>
-      <c r="AB14">
+      <c r="AD14">
         <v>34.799014929441</v>
       </c>
-      <c r="AC14">
+      <c r="AE14">
         <v>1032.37585449219</v>
       </c>
-      <c r="AD14">
+      <c r="AF14">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE14">
+      <c r="AG14">
         <v>35.239990234375</v>
       </c>
-      <c r="AF14">
+      <c r="AH14">
         <v>8.0856177694087997E-4</v>
       </c>
-      <c r="AG14" s="1">
+      <c r="AI14" s="1">
         <v>-6.3074450083429903E-5</v>
       </c>
-      <c r="AH14">
+      <c r="AJ14">
         <v>0.610162968117403</v>
       </c>
-      <c r="AI14">
+      <c r="AK14">
         <v>2.3512095569044101E-3</v>
       </c>
-      <c r="AJ14">
+      <c r="AL14">
         <v>0.966470623804495</v>
       </c>
-      <c r="AK14">
+      <c r="AM14">
         <v>3.21740385123233</v>
       </c>
-      <c r="AL14">
+      <c r="AN14">
         <v>4.8927052045729599E-2</v>
       </c>
-      <c r="AM14">
+      <c r="AO14">
         <v>5.3640965723120403E-2</v>
       </c>
-      <c r="AN14">
+      <c r="AP14">
         <v>12.4064422612822</v>
       </c>
-      <c r="AO14">
+      <c r="AQ14">
         <v>-0.108979679237727</v>
       </c>
-      <c r="AP14">
+      <c r="AR14">
         <v>0.107432105574933</v>
       </c>
-      <c r="AQ14" s="1">
+      <c r="AS14" s="1">
         <v>-7.0958756343970697E-5</v>
       </c>
-      <c r="AR14">
+      <c r="AT14">
         <v>0.18543316736702101</v>
       </c>
-      <c r="AS14">
+      <c r="AU14">
         <v>0.61051158179323795</v>
       </c>
-      <c r="AT14">
+      <c r="AV14">
         <v>0.21584843973948101</v>
       </c>
-      <c r="AU14">
+      <c r="AW14">
         <v>0.60894113294389596</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>59</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15">
         <v>126.64101434179101</v>
       </c>
-      <c r="C15">
+      <c r="E15">
         <v>152.648875067858</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>3198.2960449218699</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>0.49830727427604299</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>2368475.4198503098</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>2.96325468462652E-5</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>4.9230138970995999E-2</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>-1621.5387258119899</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>0.74043415234063303</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>-0.51963169426449296</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>2.85960889399177E-3</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>2.0000000120716899</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>10.1010101010101</v>
       </c>
-      <c r="O15">
+      <c r="Q15">
         <v>7.2278872541874706E-2</v>
       </c>
-      <c r="P15">
+      <c r="R15">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>2.12256330977331E-2</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>-505.06936753380199</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>0.72786401007440205</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>0.55667473210721796</v>
       </c>
-      <c r="V15">
+      <c r="X15">
         <v>-3.1391292031542002E-4</v>
       </c>
-      <c r="W15">
+      <c r="Y15">
         <v>2564.6298828125</v>
       </c>
-      <c r="X15">
+      <c r="Z15">
         <v>3211.919921875</v>
       </c>
-      <c r="Y15">
+      <c r="AA15">
         <v>290.66535135479398</v>
       </c>
-      <c r="Z15">
+      <c r="AB15">
         <v>2795.6762249315502</v>
       </c>
-      <c r="AA15">
+      <c r="AC15">
         <v>321.21744741137599</v>
       </c>
-      <c r="AB15">
+      <c r="AD15">
         <v>35.419949419311301</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <v>1028.84057617188</v>
       </c>
-      <c r="AD15">
+      <c r="AF15">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE15">
+      <c r="AG15">
         <v>111.199951171875</v>
       </c>
-      <c r="AF15">
+      <c r="AH15">
         <v>1.6598196618106001E-4</v>
       </c>
-      <c r="AG15" s="1">
+      <c r="AI15" s="1">
         <v>-3.6297439223404102E-5</v>
       </c>
-      <c r="AH15">
+      <c r="AJ15">
         <v>1.00353651020831</v>
       </c>
-      <c r="AI15">
+      <c r="AK15">
         <v>3.2924815142586902E-3</v>
       </c>
-      <c r="AJ15">
+      <c r="AL15">
         <v>0.92375534717320096</v>
       </c>
-      <c r="AK15">
+      <c r="AM15">
         <v>3.2174078608500301</v>
       </c>
-      <c r="AL15">
+      <c r="AN15">
         <v>6.51812667588961E-2</v>
       </c>
-      <c r="AM15">
+      <c r="AO15">
         <v>7.1545910728364304E-2</v>
       </c>
-      <c r="AN15">
+      <c r="AP15">
         <v>20.235395364819901</v>
       </c>
-      <c r="AO15">
+      <c r="AQ15">
         <v>-0.50210410384307103</v>
       </c>
-      <c r="AP15">
+      <c r="AR15">
         <v>-0.35936205227655299</v>
       </c>
-      <c r="AQ15" s="1">
+      <c r="AS15" s="1">
         <v>-4.0834619126289701E-5</v>
       </c>
-      <c r="AR15">
+      <c r="AT15">
         <v>0.30758977034263901</v>
       </c>
-      <c r="AS15">
+      <c r="AU15">
         <v>1.0041193809795199</v>
       </c>
-      <c r="AT15">
+      <c r="AV15">
         <v>0.35500981170576401</v>
       </c>
-      <c r="AU15">
+      <c r="AW15">
         <v>1.0169248280926899</v>
       </c>
     </row>
-    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16">
         <v>129.024701241201</v>
       </c>
-      <c r="C16">
+      <c r="E16">
         <v>157.311820921877</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>3474.4099609374998</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>0.62917553894137801</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>2670170.2221477102</v>
       </c>
-      <c r="G16" s="1">
+      <c r="I16" s="1">
         <v>3.7790574087407999E-5</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>4.6436310182677597E-2</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>-1842.78052508776</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>-0.30964800065048198</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>-0.63239520528225601</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>9.3143119834053999E-4</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>2.0000000244367602</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>10.1010101010101</v>
       </c>
-      <c r="O16">
+      <c r="Q16">
         <v>7.36003530395508E-2</v>
       </c>
-      <c r="P16">
+      <c r="R16">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>90</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>1.7171580940225001E-2</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>-529.53094372973896</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>0.71635810556048996</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>0.54963894645736899</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>-3.4062397112429998E-4</v>
       </c>
-      <c r="W16">
+      <c r="Y16">
         <v>2750.9599609375</v>
       </c>
-      <c r="X16">
+      <c r="Z16">
         <v>3474.669921875</v>
       </c>
-      <c r="Y16">
+      <c r="AA16">
         <v>419.860834819888</v>
       </c>
-      <c r="Z16">
+      <c r="AB16">
         <v>3151.75837315033</v>
       </c>
-      <c r="AA16">
+      <c r="AC16">
         <v>99.449314152892796</v>
       </c>
-      <c r="AB16">
+      <c r="AD16">
         <v>204.408731725221</v>
       </c>
-      <c r="AC16">
+      <c r="AE16">
         <v>1012.57690429688</v>
       </c>
-      <c r="AD16">
+      <c r="AF16">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE16">
+      <c r="AG16">
         <v>86.97998046875</v>
       </c>
-      <c r="AF16">
+      <c r="AH16">
         <v>-4.9960810153039999E-4</v>
       </c>
-      <c r="AG16">
+      <c r="AI16">
         <v>1.394659125849E-4</v>
       </c>
-      <c r="AH16">
+      <c r="AJ16">
         <v>1.35684160208093</v>
       </c>
-      <c r="AI16">
+      <c r="AK16">
         <v>4.4337293213665202E-3</v>
       </c>
-      <c r="AJ16">
+      <c r="AL16">
         <v>0.88222893839927896</v>
       </c>
-      <c r="AK16">
+      <c r="AM16">
         <v>3.2174078529278698</v>
       </c>
-      <c r="AL16">
+      <c r="AN16">
         <v>8.8643407533476104E-2</v>
       </c>
-      <c r="AM16">
+      <c r="AO16">
         <v>9.8349517379556897E-2</v>
       </c>
-      <c r="AN16">
+      <c r="AP16">
         <v>26.701148845901798</v>
       </c>
-      <c r="AO16">
+      <c r="AQ16">
         <v>-0.278265328400567</v>
       </c>
-      <c r="AP16">
+      <c r="AR16">
         <v>-0.13000267641138999</v>
       </c>
-      <c r="AQ16">
+      <c r="AS16">
         <v>1.5689915165807E-4</v>
       </c>
-      <c r="AR16">
+      <c r="AT16">
         <v>0.41747503670298403</v>
       </c>
-      <c r="AS16">
+      <c r="AU16">
         <v>1.3577307930473701</v>
       </c>
-      <c r="AT16">
+      <c r="AV16">
         <v>0.48003032539476198</v>
       </c>
-      <c r="AU16">
+      <c r="AW16">
         <v>1.3541622759927401</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17">
         <v>47.892650049031303</v>
       </c>
-      <c r="C17">
+      <c r="E17">
         <v>59.448300162100203</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>2801.4139648437499</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <v>0.35064591714358101</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>2235515.6406285302</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>6.3227807946266906E-5</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>2.1785349958175101E-2</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>-1784.86752066853</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>-0.301635222510242</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>-0.35977474697904499</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>8.9962439949339296E-3</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>2.0000000256644399</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>10.1010101010101</v>
       </c>
-      <c r="O17">
+      <c r="Q17">
         <v>6.8603572335970905E-2</v>
       </c>
-      <c r="P17">
+      <c r="R17">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>90</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>2.0830166039769601E-2</v>
       </c>
-      <c r="S17">
+      <c r="U17">
         <v>-488.88424587531199</v>
       </c>
-      <c r="T17">
+      <c r="V17">
         <v>0.72986505572028204</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>0.55805355454829197</v>
       </c>
-      <c r="V17">
+      <c r="X17">
         <v>-5.1765843972430997E-4</v>
       </c>
-      <c r="W17">
+      <c r="Y17">
         <v>2489.64990234375</v>
       </c>
-      <c r="X17">
+      <c r="Z17">
         <v>2801.46997070312</v>
       </c>
-      <c r="Y17">
+      <c r="AA17">
         <v>140.53821094000301</v>
       </c>
-      <c r="Z17">
+      <c r="AB17">
         <v>2641.6795427754701</v>
       </c>
-      <c r="AA17">
+      <c r="AC17">
         <v>82.679174714660306</v>
       </c>
-      <c r="AB17">
+      <c r="AD17">
         <v>88.608515821596896</v>
       </c>
-      <c r="AC17">
+      <c r="AE17">
         <v>1031.66906738281</v>
       </c>
-      <c r="AD17">
+      <c r="AF17">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE17">
+      <c r="AG17">
         <v>72.64990234375</v>
       </c>
-      <c r="AF17">
+      <c r="AH17">
         <v>6.6934829400209996E-4</v>
       </c>
-      <c r="AG17" s="1">
+      <c r="AI17" s="1">
         <v>2.0700349453860798E-5</v>
       </c>
-      <c r="AH17">
+      <c r="AJ17">
         <v>0.69750674594105999</v>
       </c>
-      <c r="AI17">
+      <c r="AK17">
         <v>2.3394188652532699E-3</v>
       </c>
-      <c r="AJ17">
+      <c r="AL17">
         <v>0.95806953265522299</v>
       </c>
-      <c r="AK17">
+      <c r="AM17">
         <v>3.21740787216289</v>
       </c>
-      <c r="AL17">
+      <c r="AN17">
         <v>5.1752231595456097E-2</v>
       </c>
-      <c r="AM17">
+      <c r="AO17">
         <v>5.7297818522903901E-2</v>
       </c>
-      <c r="AN17">
+      <c r="AP17">
         <v>14.300607747153</v>
       </c>
-      <c r="AO17">
+      <c r="AQ17">
         <v>-0.32118870334008698</v>
       </c>
-      <c r="AP17">
+      <c r="AR17">
         <v>-4.2348972588692101E-2</v>
       </c>
-      <c r="AQ17" s="1">
+      <c r="AS17" s="1">
         <v>2.3287893135585101E-5</v>
       </c>
-      <c r="AR17">
+      <c r="AT17">
         <v>0.212976018380506</v>
       </c>
-      <c r="AS17">
+      <c r="AU17">
         <v>0.69774359125521601</v>
       </c>
-      <c r="AT17">
+      <c r="AV17">
         <v>0.24668961245306101</v>
       </c>
-      <c r="AU17">
+      <c r="AW17">
         <v>0.69735849943773898</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18">
         <v>103.113719350845</v>
       </c>
-      <c r="C18">
+      <c r="E18">
         <v>129.918642507908</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <v>3177.3040039062498</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <v>0.48350791825434403</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>2415207.6139438502</v>
       </c>
-      <c r="G18" s="1">
+      <c r="I18" s="1">
         <v>3.6373324979952398E-5</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>4.1678529870478202E-2</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>-1697.75185966203</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>0.63906279706680302</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>-0.30282498366076499</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>4.0608097945921398E-3</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>2.0000000148688</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>10.1010101010101</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>7.4958259674783201E-2</v>
       </c>
-      <c r="P18">
+      <c r="R18">
         <v>141.414141414141</v>
       </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
         <v>1.8676560800543099E-2</v>
       </c>
-      <c r="S18">
+      <c r="U18">
         <v>-512.38309499984405</v>
       </c>
-      <c r="T18">
+      <c r="V18">
         <v>0.72907460339639696</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>0.557362545669283</v>
       </c>
-      <c r="V18">
+      <c r="X18">
         <v>-3.5388155818056E-4</v>
       </c>
-      <c r="W18">
+      <c r="Y18">
         <v>2611.05004882812</v>
       </c>
-      <c r="X18">
+      <c r="Z18">
         <v>3177.8798828125</v>
       </c>
-      <c r="Y18">
+      <c r="AA18">
         <v>284.58100988638699</v>
       </c>
-      <c r="Z18">
+      <c r="AB18">
         <v>2851.3497899322601</v>
       </c>
-      <c r="AA18">
+      <c r="AC18">
         <v>203.89806614233299</v>
       </c>
-      <c r="AB18">
+      <c r="AD18">
         <v>78.359037540650704</v>
       </c>
-      <c r="AC18">
+      <c r="AE18">
         <v>1030.5517578125</v>
       </c>
-      <c r="AD18">
+      <c r="AF18">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE18">
+      <c r="AG18">
         <v>60.719970703125</v>
       </c>
-      <c r="AF18">
+      <c r="AH18">
         <v>-8.1959611224836004E-4</v>
       </c>
-      <c r="AG18">
+      <c r="AI18">
         <v>1.1953075784872001E-4</v>
       </c>
-      <c r="AH18">
+      <c r="AJ18">
         <v>0.99219160202485601</v>
       </c>
-      <c r="AI18">
+      <c r="AK18">
         <v>4.01840375200302E-3</v>
       </c>
-      <c r="AJ18">
+      <c r="AL18">
         <v>0.92822736427243302</v>
       </c>
-      <c r="AK18">
+      <c r="AM18">
         <v>3.2174078636613799</v>
       </c>
-      <c r="AL18">
+      <c r="AN18">
         <v>7.1335861937626102E-2</v>
       </c>
-      <c r="AM18">
+      <c r="AO18">
         <v>7.9323152481862794E-2</v>
       </c>
-      <c r="AN18">
+      <c r="AP18">
         <v>19.895247299509201</v>
       </c>
-      <c r="AO18">
+      <c r="AQ18">
         <v>-0.21498972997969501</v>
       </c>
-      <c r="AP18">
+      <c r="AR18">
         <v>0.43699819702278803</v>
       </c>
-      <c r="AQ18">
+      <c r="AS18">
         <v>1.3447210257973001E-4</v>
       </c>
-      <c r="AR18">
+      <c r="AT18">
         <v>0.30334395463367197</v>
       </c>
-      <c r="AS18">
+      <c r="AU18">
         <v>0.99277498868291603</v>
       </c>
-      <c r="AT18">
+      <c r="AV18">
         <v>0.35099896334499697</v>
       </c>
-      <c r="AU18">
+      <c r="AW18">
         <v>0.995799843694675</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19">
         <v>109.05698891906501</v>
       </c>
-      <c r="C19">
+      <c r="E19">
         <v>132.14211224765799</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>3114.6000488281302</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <v>0.50138116364421903</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>2356811.01120112</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>3.7032584514455203E-5</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>4.3578609885172898E-2</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>-1676.13878148138</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>0.56610666632196405</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>-0.57740282623788397</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>3.2865357140801502E-3</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>2.0000000146407402</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>10.1010101010101</v>
       </c>
-      <c r="O19">
+      <c r="Q19">
         <v>5.9647926438254603E-2</v>
       </c>
-      <c r="P19">
+      <c r="R19">
         <v>101.010101010101</v>
       </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>2.0362513936303402E-2</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>-502.99178689447899</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>0.73236612528785905</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>0.55911984044832497</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>-3.2849761487373003E-4</v>
       </c>
-      <c r="W19">
+      <c r="Y19">
         <v>2561.6201171875</v>
       </c>
-      <c r="X19">
+      <c r="Z19">
         <v>3144.169921875</v>
       </c>
-      <c r="Y19">
+      <c r="AA19">
         <v>309.91374528457999</v>
       </c>
-      <c r="Z19">
+      <c r="AB19">
         <v>2782.8704946002299</v>
       </c>
-      <c r="AA19">
+      <c r="AC19">
         <v>232.20795604901099</v>
       </c>
-      <c r="AB19">
+      <c r="AD19">
         <v>40.439455317017703</v>
       </c>
-      <c r="AC19">
+      <c r="AE19">
         <v>1035.20434570312</v>
       </c>
-      <c r="AD19">
+      <c r="AF19">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE19">
+      <c r="AG19">
         <v>111.89990234375</v>
       </c>
-      <c r="AF19">
+      <c r="AH19">
         <v>-5.9915530530028004E-4</v>
       </c>
-      <c r="AG19">
+      <c r="AI19">
         <v>-1.2417841521492E-4</v>
       </c>
-      <c r="AH19">
+      <c r="AJ19">
         <v>1.03442750060454</v>
       </c>
-      <c r="AI19">
+      <c r="AK19">
         <v>3.2945120300983E-3</v>
       </c>
-      <c r="AJ19">
+      <c r="AL19">
         <v>0.920849949372198</v>
       </c>
-      <c r="AK19">
+      <c r="AM19">
         <v>3.2174078600465998</v>
       </c>
-      <c r="AL19">
+      <c r="AN19">
         <v>6.9300697940015199E-2</v>
       </c>
-      <c r="AM19">
+      <c r="AO19">
         <v>7.6702400359055595E-2</v>
       </c>
-      <c r="AN19">
+      <c r="AP19">
         <v>20.805840725988201</v>
       </c>
-      <c r="AO19">
+      <c r="AQ19">
         <v>0.171088584123267</v>
       </c>
-      <c r="AP19">
+      <c r="AR19">
         <v>0.54316776821813695</v>
       </c>
-      <c r="AQ19">
+      <c r="AS19">
         <v>-1.3970071711681001E-4</v>
       </c>
-      <c r="AR19">
+      <c r="AT19">
         <v>0.31722915219125802</v>
       </c>
-      <c r="AS19">
+      <c r="AU19">
         <v>1.03486727191307</v>
       </c>
-      <c r="AT19">
+      <c r="AV19">
         <v>0.365880832798894</v>
       </c>
-      <c r="AU19">
+      <c r="AW19">
         <v>1.0453744055851999</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>64</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20">
         <v>8.7151404087093507</v>
       </c>
-      <c r="C20">
+      <c r="E20">
         <v>10.595102634860099</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>1669.6919921875001</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <v>6.9968657252859903E-2</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>1392849.6038587401</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>9.9050386801228005E-5</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>6.3712696990031199E-3</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>-1199.33880233428</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>-0.204948884292598</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>-0.74110552247081496</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>6.6351334746913198E-3</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>2.0000000502519901</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>10.1010101010101</v>
       </c>
-      <c r="O20">
+      <c r="Q20">
         <v>6.6626052935950406E-2</v>
       </c>
-      <c r="P20">
+      <c r="R20">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>90</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>2.85641239972916E-2</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>-322.23608181966102</v>
       </c>
-      <c r="T20">
+      <c r="V20">
         <v>0.72786401007440205</v>
       </c>
-      <c r="U20">
+      <c r="W20">
         <v>0.55712004702124795</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>-6.1833645492381003E-4</v>
       </c>
-      <c r="W20">
+      <c r="Y20">
         <v>1621.41003417969</v>
       </c>
-      <c r="X20">
+      <c r="Z20">
         <v>1671.11999511719</v>
       </c>
-      <c r="Y20">
+      <c r="AA20">
         <v>28.972560334900201</v>
       </c>
-      <c r="Z20">
+      <c r="AB20">
         <v>1646.3325716663101</v>
       </c>
-      <c r="AA20">
+      <c r="AC20">
         <v>9.5690931592409907</v>
       </c>
-      <c r="AB20">
+      <c r="AD20">
         <v>11.168585368593799</v>
       </c>
-      <c r="AC20">
+      <c r="AE20">
         <v>1028.84057617188</v>
       </c>
-      <c r="AD20">
+      <c r="AF20">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE20">
+      <c r="AG20">
         <v>8.1700439453125</v>
       </c>
-      <c r="AF20" s="1">
+      <c r="AH20" s="1">
         <v>-5.9511786368764701E-5</v>
       </c>
-      <c r="AG20" s="1">
+      <c r="AI20" s="1">
         <v>1.0700864905912101E-5</v>
       </c>
-      <c r="AH20">
+      <c r="AJ20">
         <v>0.12806409257569101</v>
       </c>
-      <c r="AI20">
+      <c r="AK20">
         <v>1.0249293095322E-4</v>
       </c>
-      <c r="AJ20">
+      <c r="AL20">
         <v>0.99835820978259904</v>
       </c>
-      <c r="AK20">
+      <c r="AM20">
         <v>3.2174078853185399</v>
       </c>
-      <c r="AL20">
+      <c r="AN20">
         <v>1.06139437790762E-2</v>
       </c>
-      <c r="AM20">
+      <c r="AO20">
         <v>1.2109786794875401E-2</v>
       </c>
-      <c r="AN20">
+      <c r="AP20">
         <v>2.70389737385706</v>
       </c>
-      <c r="AO20">
+      <c r="AQ20">
         <v>-0.148016712809243</v>
       </c>
-      <c r="AP20">
+      <c r="AR20">
         <v>0.34487988680042198</v>
       </c>
-      <c r="AQ20" s="1">
+      <c r="AS20" s="1">
         <v>1.2038473019137499E-5</v>
       </c>
-      <c r="AR20">
+      <c r="AT20">
         <v>3.8753713557893199E-2</v>
       </c>
-      <c r="AS20">
+      <c r="AU20">
         <v>0.12813324264780299</v>
       </c>
-      <c r="AT20">
+      <c r="AV20">
         <v>4.5301942385805198E-2</v>
       </c>
-      <c r="AU20">
+      <c r="AW20">
         <v>0.127219554443043</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>65</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21">
         <v>6.6998207545491599</v>
       </c>
-      <c r="C21">
+      <c r="E21">
         <v>8.1918709815307</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>1666.5739990234399</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <v>7.4565364279617893E-2</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1396263.12861177</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>1.4724540004369999E-4</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>4.92593005058653E-3</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>-1207.8557269139601</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>-0.20031468733932001</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>-0.61856261679743896</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>7.0207690138215702E-3</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>2.0000001036784201</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>10.1010101010101</v>
       </c>
-      <c r="O21">
+      <c r="Q21">
         <v>6.9361804731884399E-2</v>
       </c>
-      <c r="P21">
+      <c r="R21">
         <v>141.414141414141</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>90</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>3.2605206035744801E-2</v>
       </c>
-      <c r="S21">
+      <c r="U21">
         <v>-323.67982016601599</v>
       </c>
-      <c r="T21">
+      <c r="V21">
         <v>0.72786401007440205</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>0.55691878523376703</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>-8.7058312818047998E-4</v>
       </c>
-      <c r="W21">
+      <c r="Y21">
         <v>1627.63000488281</v>
       </c>
-      <c r="X21">
+      <c r="Z21">
         <v>1671.06994628906</v>
       </c>
-      <c r="Y21">
+      <c r="AA21">
         <v>20.7911308899536</v>
       </c>
-      <c r="Z21">
+      <c r="AB21">
         <v>1650.4269728136901</v>
       </c>
-      <c r="AA21">
+      <c r="AC21">
         <v>10.248739900634501</v>
       </c>
-      <c r="AB21">
+      <c r="AD21">
         <v>12.408911286680899</v>
       </c>
-      <c r="AC21">
+      <c r="AE21">
         <v>1028.84057617188</v>
       </c>
-      <c r="AD21">
+      <c r="AF21">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE21">
+      <c r="AG21">
         <v>8.0599365234375</v>
       </c>
-      <c r="AF21" s="1">
+      <c r="AH21" s="1">
         <v>-4.4236639911479499E-5</v>
       </c>
-      <c r="AG21" s="1">
+      <c r="AI21" s="1">
         <v>-5.2128129912688496E-6</v>
       </c>
-      <c r="AH21">
+      <c r="AJ21">
         <v>0.137819608204646</v>
       </c>
-      <c r="AI21">
+      <c r="AK21">
         <v>1.4356283141814E-4</v>
       </c>
-      <c r="AJ21">
+      <c r="AL21">
         <v>0.99812576760634997</v>
       </c>
-      <c r="AK21">
+      <c r="AM21">
         <v>3.2174078851507701</v>
       </c>
-      <c r="AL21">
+      <c r="AN21">
         <v>1.18103576768632E-2</v>
       </c>
-      <c r="AM21">
+      <c r="AO21">
         <v>1.3525068876813401E-2</v>
       </c>
-      <c r="AN21">
+      <c r="AP21">
         <v>2.88677051766064</v>
       </c>
-      <c r="AO21">
+      <c r="AQ21">
         <v>-0.107915026961236</v>
       </c>
-      <c r="AP21">
+      <c r="AR21">
         <v>0.27373088571188298</v>
       </c>
-      <c r="AQ21" s="1">
+      <c r="AS21" s="1">
         <v>-5.8644146152064197E-6</v>
       </c>
-      <c r="AR21">
+      <c r="AT21">
         <v>4.1548546901151402E-2</v>
       </c>
-      <c r="AS21">
+      <c r="AU21">
         <v>0.13786824615226001</v>
       </c>
-      <c r="AT21">
+      <c r="AV21">
         <v>4.8743785882216201E-2</v>
       </c>
-      <c r="AU21">
+      <c r="AW21">
         <v>0.13635973728964701</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>66</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22">
         <v>6.14791407645028</v>
       </c>
-      <c r="C22">
+      <c r="E22">
         <v>7.57107222360034</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>1683.30200195312</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <v>8.1462302611495702E-2</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1406757.0368765199</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>2.4093285145186999E-4</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>4.5159989404117799E-3</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>-1220.3787124263599</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>0.32324574135696599</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>-0.50017389757904196</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>1.0473220602297099E-2</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>2.00000012780629</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>10.1010101010101</v>
       </c>
-      <c r="O22">
+      <c r="Q22">
         <v>5.7953765585910803E-2</v>
       </c>
-      <c r="P22">
+      <c r="R22">
         <v>111.111111111111</v>
       </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
         <v>2.5023068380157901E-2</v>
       </c>
-      <c r="S22">
+      <c r="U22">
         <v>-327.72549393960901</v>
       </c>
-      <c r="T22">
+      <c r="V22">
         <v>0.72736364071303605</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>0.556278081006639</v>
       </c>
-      <c r="V22">
+      <c r="X22">
         <v>-1.8307895985100299E-3</v>
       </c>
-      <c r="W22">
+      <c r="Y22">
         <v>1646.30004882812</v>
       </c>
-      <c r="X22">
+      <c r="Z22">
         <v>1683.41003417969</v>
       </c>
-      <c r="Y22">
+      <c r="AA22">
         <v>18.174696382197698</v>
       </c>
-      <c r="Z22">
+      <c r="AB22">
         <v>1662.8256469446701</v>
       </c>
-      <c r="AA22">
+      <c r="AC22">
         <v>12.2684418220224</v>
       </c>
-      <c r="AB22">
+      <c r="AD22">
         <v>6.6790243204347899</v>
       </c>
-      <c r="AC22">
+      <c r="AE22">
         <v>1028.13330078125</v>
       </c>
-      <c r="AD22">
+      <c r="AF22">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE22">
+      <c r="AG22">
         <v>6.9100341796875</v>
       </c>
-      <c r="AF22">
+      <c r="AH22">
         <v>4.055971036593E-4</v>
       </c>
-      <c r="AG22" s="1">
+      <c r="AI22" s="1">
         <v>5.2021512161155802E-6</v>
       </c>
-      <c r="AH22">
+      <c r="AJ22">
         <v>0.152749071493094</v>
       </c>
-      <c r="AI22">
+      <c r="AK22">
         <v>1.4311674491388E-4</v>
       </c>
-      <c r="AJ22">
+      <c r="AL22">
         <v>0.99771827008599201</v>
       </c>
-      <c r="AK22">
+      <c r="AM22">
         <v>3.21740788486292</v>
       </c>
-      <c r="AL22">
+      <c r="AN22">
         <v>1.27377919688666E-2</v>
       </c>
-      <c r="AM22">
+      <c r="AO22">
         <v>1.4519710673173199E-2</v>
       </c>
-      <c r="AN22">
+      <c r="AP22">
         <v>3.18868611024932</v>
       </c>
-      <c r="AO22">
+      <c r="AQ22">
         <v>-0.17942192712437199</v>
       </c>
-      <c r="AP22">
+      <c r="AR22">
         <v>0.12453841009747101</v>
       </c>
-      <c r="AQ22" s="1">
+      <c r="AS22" s="1">
         <v>5.8524201181873497E-6</v>
       </c>
-      <c r="AR22">
+      <c r="AT22">
         <v>4.6020849170228098E-2</v>
       </c>
-      <c r="AS22">
+      <c r="AU22">
         <v>0.15283931733248499</v>
       </c>
-      <c r="AT22">
+      <c r="AV22">
         <v>5.4036858858788103E-2</v>
       </c>
-      <c r="AU22">
+      <c r="AW22">
         <v>0.15387898819163301</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>67</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23">
         <v>9.2727236980997496</v>
       </c>
-      <c r="C23">
+      <c r="E23">
         <v>10.8838796481442</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>1657.1559814453101</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <v>6.7419738263246001E-2</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1385722.4988212101</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>1.1965512090884001E-4</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>6.5829254597394296E-3</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>-1194.9568194082999</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>-0.35140079876545499</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>-1.00805273505877</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>8.4537015881627695E-3</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>2.0000000530312998</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>10.1010101010101</v>
       </c>
-      <c r="O23">
+      <c r="Q23">
         <v>6.0116557620927998E-2</v>
       </c>
-      <c r="P23">
+      <c r="R23">
         <v>101.010101010101</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>90</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>2.5953905931188601E-2</v>
       </c>
-      <c r="S23">
+      <c r="U23">
         <v>-320.96874076015598</v>
       </c>
-      <c r="T23">
+      <c r="V23">
         <v>0.72736364071303605</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>0.55675383779154897</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>-7.9434403223947996E-4</v>
       </c>
-      <c r="W23">
+      <c r="Y23">
         <v>1614.11999511719</v>
       </c>
-      <c r="X23">
+      <c r="Z23">
         <v>1657.69995117188</v>
       </c>
-      <c r="Y23">
+      <c r="AA23">
         <v>28.430185486775599</v>
       </c>
-      <c r="Z23">
+      <c r="AB23">
         <v>1637.9666417411499</v>
       </c>
-      <c r="AA23">
+      <c r="AC23">
         <v>3.6096935093382898</v>
       </c>
-      <c r="AB23">
+      <c r="AD23">
         <v>11.5482002521385</v>
       </c>
-      <c r="AC23">
+      <c r="AE23">
         <v>1028.13330078125</v>
       </c>
-      <c r="AD23">
+      <c r="AF23">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE23">
+      <c r="AG23">
         <v>4.3499755859375</v>
       </c>
-      <c r="AF23" s="1">
+      <c r="AH23" s="1">
         <v>7.49656960487446E-5</v>
       </c>
-      <c r="AG23" s="1">
+      <c r="AI23" s="1">
         <v>-4.65706881202576E-7</v>
       </c>
-      <c r="AH23">
+      <c r="AJ23">
         <v>0.120118316598015</v>
       </c>
-      <c r="AI23">
+      <c r="AK23">
         <v>1.1651267399784E-4</v>
       </c>
-      <c r="AJ23">
+      <c r="AL23">
         <v>0.99837710805677404</v>
       </c>
-      <c r="AK23">
+      <c r="AM23">
         <v>3.2174078853082602</v>
       </c>
-      <c r="AL23">
+      <c r="AN23">
         <v>1.06466312640584E-2</v>
       </c>
-      <c r="AM23">
+      <c r="AO23">
         <v>1.19267637112517E-2</v>
       </c>
-      <c r="AN23">
+      <c r="AP23">
         <v>2.4953163313606299</v>
       </c>
-      <c r="AO23">
+      <c r="AQ23">
         <v>-0.179667527392225</v>
       </c>
-      <c r="AP23">
+      <c r="AR23">
         <v>-0.23560254556443</v>
       </c>
-      <c r="AQ23" s="1">
+      <c r="AS23" s="1">
         <v>-5.2392024136718002E-7</v>
       </c>
-      <c r="AR23">
+      <c r="AT23">
         <v>3.6182140224468397E-2</v>
       </c>
-      <c r="AS23">
+      <c r="AU23">
         <v>0.120172237570564</v>
       </c>
-      <c r="AT23">
+      <c r="AV23">
         <v>4.2487302048209698E-2</v>
       </c>
-      <c r="AU23">
+      <c r="AW23">
         <v>0.118985720191479</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>68</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24">
         <v>5.0042729255860001</v>
       </c>
-      <c r="C24">
+      <c r="E24">
         <v>6.17858988538784</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>1657.72998046875</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <v>6.3615212013754405E-2</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1392808.90499837</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>2.0760389913206001E-4</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>3.7343473832346001E-3</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>-1211.68657961811</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>-0.720258566934179</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>-0.136371304408269</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>1.7708454026913401E-2</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>2.0000000925757901</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>10.1010101010101</v>
       </c>
-      <c r="O24">
+      <c r="Q24">
         <v>6.95858072563382E-2</v>
       </c>
-      <c r="P24">
+      <c r="R24">
         <v>131.31313131313101</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>90</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>2.9452639837705501E-2</v>
       </c>
-      <c r="S24">
+      <c r="U24">
         <v>-323.403413909167</v>
       </c>
-      <c r="T24">
+      <c r="V24">
         <v>0.72736364071303605</v>
       </c>
-      <c r="U24">
+      <c r="W24">
         <v>0.55680552420210805</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>-1.2378690687196701E-3</v>
       </c>
-      <c r="W24">
+      <c r="Y24">
         <v>1626.68005371094</v>
       </c>
-      <c r="X24">
+      <c r="Z24">
         <v>1657.90002441406</v>
       </c>
-      <c r="Y24">
+      <c r="AA24">
         <v>14.942319425379999</v>
       </c>
-      <c r="Z24">
+      <c r="AB24">
         <v>1646.3692486008999</v>
       </c>
-      <c r="AA24">
+      <c r="AC24">
         <v>2.9397853552245601</v>
       </c>
-      <c r="AB24">
+      <c r="AD24">
         <v>13.348411742738801</v>
       </c>
-      <c r="AC24">
+      <c r="AE24">
         <v>1028.13330078125</v>
       </c>
-      <c r="AD24">
+      <c r="AF24">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE24">
+      <c r="AG24">
         <v>3.3699951171875</v>
       </c>
-      <c r="AF24">
+      <c r="AH24">
         <v>2.4929233444863998E-4</v>
       </c>
-      <c r="AG24" s="1">
+      <c r="AI24" s="1">
         <v>-8.2551868787308397E-6</v>
       </c>
-      <c r="AH24">
+      <c r="AJ24">
         <v>0.103218241464873</v>
       </c>
-      <c r="AI24">
+      <c r="AK24">
         <v>1.3918373819919001E-4</v>
       </c>
-      <c r="AJ24">
+      <c r="AL24">
         <v>0.99878743769403799</v>
       </c>
-      <c r="AK24">
+      <c r="AM24">
         <v>3.2174078856796702</v>
       </c>
-      <c r="AL24">
+      <c r="AN24">
         <v>1.16196127999661E-2</v>
       </c>
-      <c r="AM24">
+      <c r="AO24">
         <v>1.33022264977851E-2</v>
       </c>
-      <c r="AN24">
+      <c r="AP24">
         <v>1.9673107229637099</v>
       </c>
-      <c r="AO24">
+      <c r="AQ24">
         <v>-0.13442617344746299</v>
       </c>
-      <c r="AP24">
+      <c r="AR24">
         <v>-8.5224296305851502E-2</v>
       </c>
-      <c r="AQ24" s="1">
+      <c r="AS24" s="1">
         <v>-9.2870852386165998E-6</v>
       </c>
-      <c r="AR24">
+      <c r="AT24">
         <v>3.06942281118797E-2</v>
       </c>
-      <c r="AS24">
+      <c r="AU24">
         <v>0.103225854172373</v>
       </c>
-      <c r="AT24">
+      <c r="AV24">
         <v>3.64958507394606E-2</v>
       </c>
-      <c r="AU24">
+      <c r="AW24">
         <v>9.7497475272894693E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25">
         <v>7.9161226719114897</v>
       </c>
-      <c r="C25">
+      <c r="E25">
         <v>9.5123306563557808</v>
       </c>
-      <c r="D25">
+      <c r="F25">
         <v>1685.78400878906</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <v>7.3554686960425594E-2</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>1399049.16122965</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>9.1980381989697005E-5</v>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>5.6988044131056296E-3</v>
       </c>
-      <c r="I25">
+      <c r="K25">
         <v>-1207.5103220682599</v>
       </c>
-      <c r="J25">
+      <c r="L25">
         <v>0.21681733900575201</v>
       </c>
-      <c r="K25">
+      <c r="M25">
         <v>-0.53819108139879801</v>
       </c>
-      <c r="L25">
+      <c r="N25">
         <v>1.32930397164565E-2</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>2.0000000606838602</v>
       </c>
-      <c r="N25">
+      <c r="P25">
         <v>10.1010101010101</v>
       </c>
-      <c r="O25">
+      <c r="Q25">
         <v>7.3394390065053397E-2</v>
       </c>
-      <c r="P25">
+      <c r="R25">
         <v>151.51515151515201</v>
       </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
         <v>2.25272106957994E-2</v>
       </c>
-      <c r="S25">
+      <c r="U25">
         <v>-324.73806552734402</v>
       </c>
-      <c r="T25">
+      <c r="V25">
         <v>0.72636307471013695</v>
       </c>
-      <c r="U25">
+      <c r="W25">
         <v>0.55577805708494199</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>-1.0161393838143101E-3</v>
       </c>
-      <c r="W25">
+      <c r="Y25">
         <v>1631.58996582031</v>
       </c>
-      <c r="X25">
+      <c r="Z25">
         <v>1685.81994628906</v>
       </c>
-      <c r="Y25">
+      <c r="AA25">
         <v>27.546317340462299</v>
       </c>
-      <c r="Z25">
+      <c r="AB25">
         <v>1653.6931490505899</v>
       </c>
-      <c r="AA25">
+      <c r="AC25">
         <v>18.479211576111101</v>
       </c>
-      <c r="AB25">
+      <c r="AD25">
         <v>8.2093626049811501</v>
       </c>
-      <c r="AC25">
+      <c r="AE25">
         <v>1026.71899414062</v>
       </c>
-      <c r="AD25">
+      <c r="AF25">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE25">
+      <c r="AG25">
         <v>16.639892578125</v>
       </c>
-      <c r="AF25">
+      <c r="AH25">
         <v>2.7632975218939E-4</v>
       </c>
-      <c r="AG25" s="1">
+      <c r="AI25" s="1">
         <v>8.4947642349263606E-8</v>
       </c>
-      <c r="AH25">
+      <c r="AJ25">
         <v>0.13415706473335101</v>
       </c>
-      <c r="AI25">
+      <c r="AK25">
         <v>1.4935910373609001E-4</v>
       </c>
-      <c r="AJ25">
+      <c r="AL25">
         <v>0.99830004422964103</v>
       </c>
-      <c r="AK25">
+      <c r="AM25">
         <v>3.2174078853210801</v>
       </c>
-      <c r="AL25">
+      <c r="AN25">
         <v>1.31360588115319E-2</v>
       </c>
-      <c r="AM25">
+      <c r="AO25">
         <v>1.4850514352142101E-2</v>
       </c>
-      <c r="AN25">
+      <c r="AP25">
         <v>2.7034648235214398</v>
       </c>
-      <c r="AO25">
+      <c r="AQ25">
         <v>-9.7009241208914396E-2</v>
       </c>
-      <c r="AP25">
+      <c r="AR25">
         <v>0.19256700389299</v>
       </c>
-      <c r="AQ25" s="1">
+      <c r="AS25" s="1">
         <v>9.5566097664387396E-8</v>
       </c>
-      <c r="AR25">
+      <c r="AT25">
         <v>4.0198414881775897E-2</v>
       </c>
-      <c r="AS25">
+      <c r="AU25">
         <v>0.13422511537985601</v>
       </c>
-      <c r="AT25">
+      <c r="AV25">
         <v>4.7455744645248099E-2</v>
       </c>
-      <c r="AU25">
+      <c r="AW25">
         <v>0.13263436528321301</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>70</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26">
         <v>8.6667327986460592</v>
       </c>
-      <c r="C26">
+      <c r="E26">
         <v>10.559926079508401</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>1663.27800292969</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <v>7.2906654782082095E-2</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>1385400.6063399301</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>9.6876149513747193E-5</v>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>6.3847476837457602E-3</v>
       </c>
-      <c r="I26">
+      <c r="K26">
         <v>-1191.67322024333</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>-0.204634336278809</v>
       </c>
-      <c r="K26">
+      <c r="M26">
         <v>-0.60541924694601301</v>
       </c>
-      <c r="L26">
+      <c r="N26">
         <v>4.4246735673990102E-3</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>2.0000000552556201</v>
       </c>
-      <c r="N26">
+      <c r="P26">
         <v>10.1010101010101</v>
       </c>
-      <c r="O26">
+      <c r="Q26">
         <v>6.2030603429922802E-2</v>
       </c>
-      <c r="P26">
+      <c r="R26">
         <v>121.212121212121</v>
       </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
         <v>2.1749068908065099E-2</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>-320.14922560221402</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>0.72686353043142105</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>0.556278081006639</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>-9.4359549561115995E-4</v>
       </c>
-      <c r="W26">
+      <c r="Y26">
         <v>1610.93994140625</v>
       </c>
-      <c r="X26">
+      <c r="Z26">
         <v>1663.31994628906</v>
       </c>
-      <c r="Y26">
+      <c r="AA26">
         <v>28.222432160592199</v>
       </c>
-      <c r="Z26">
+      <c r="AB26">
         <v>1637.5580177746599</v>
       </c>
-      <c r="AA26">
+      <c r="AC26">
         <v>10.779250490845</v>
       </c>
-      <c r="AB26">
+      <c r="AD26">
         <v>13.388671563106501</v>
       </c>
-      <c r="AC26">
+      <c r="AE26">
         <v>1027.42639160156</v>
       </c>
-      <c r="AD26">
+      <c r="AF26">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE26">
+      <c r="AG26">
         <v>9.389892578125</v>
       </c>
-      <c r="AF26" s="1">
+      <c r="AH26" s="1">
         <v>4.1764859236347602E-5</v>
       </c>
-      <c r="AG26" s="1">
+      <c r="AI26" s="1">
         <v>2.9330652101247702E-6</v>
       </c>
-      <c r="AH26">
+      <c r="AJ26">
         <v>0.13857998077463199</v>
       </c>
-      <c r="AI26">
+      <c r="AK26">
         <v>1.1049317704993E-4</v>
       </c>
-      <c r="AJ26">
+      <c r="AL26">
         <v>0.99812877936214806</v>
       </c>
-      <c r="AK26">
+      <c r="AM26">
         <v>3.2174078851008701</v>
       </c>
-      <c r="AL26">
+      <c r="AN26">
         <v>1.08014084702578E-2</v>
       </c>
-      <c r="AM26">
+      <c r="AO26">
         <v>1.22525450252799E-2</v>
       </c>
-      <c r="AN26">
+      <c r="AP26">
         <v>2.9733886841044401</v>
       </c>
-      <c r="AO26">
+      <c r="AQ26">
         <v>-0.11399148074502501</v>
       </c>
-      <c r="AP26">
+      <c r="AR26">
         <v>0.24941311806060701</v>
       </c>
-      <c r="AQ26" s="1">
+      <c r="AS26" s="1">
         <v>3.2996983614287899E-6</v>
       </c>
-      <c r="AR26">
+      <c r="AT26">
         <v>4.1973173802684699E-2</v>
       </c>
-      <c r="AS26">
+      <c r="AU26">
         <v>0.13866059406942999</v>
       </c>
-      <c r="AT26">
+      <c r="AV26">
         <v>4.9023923174878199E-2</v>
       </c>
-      <c r="AU26">
+      <c r="AW26">
         <v>0.139692734729361</v>
       </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>71</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27">
         <v>10.064366084067601</v>
       </c>
-      <c r="C27">
+      <c r="E27">
         <v>11.204866600076</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>1665.833984375</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <v>6.4407856886608106E-2</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>1390033.5594027999</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>1.0165280247183E-4</v>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>6.7593259271216E-3</v>
       </c>
-      <c r="I27">
+      <c r="K27">
         <v>-1200.2459698811799</v>
       </c>
-      <c r="J27">
+      <c r="L27">
         <v>-0.19423584199472299</v>
       </c>
-      <c r="K27">
+      <c r="M27">
         <v>-1.3475995954109401</v>
       </c>
-      <c r="L27">
+      <c r="N27">
         <v>1.0599596947047801E-2</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>2.0000000567993599</v>
       </c>
-      <c r="N27">
+      <c r="P27">
         <v>10.1010101010101</v>
       </c>
-      <c r="O27">
+      <c r="Q27">
         <v>6.23264130190858E-2</v>
       </c>
-      <c r="P27">
+      <c r="R27">
         <v>161.616161616162</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>90</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>4.3326361760597003E-2</v>
       </c>
-      <c r="S27">
+      <c r="U27">
         <v>-322.56644806315097</v>
       </c>
-      <c r="T27">
+      <c r="V27">
         <v>0.72786401007440205</v>
       </c>
-      <c r="U27">
+      <c r="W27">
         <v>0.55727454491346096</v>
       </c>
-      <c r="V27">
+      <c r="X27">
         <v>-1.2156662481802899E-3</v>
       </c>
-      <c r="W27">
+      <c r="Y27">
         <v>1620.68994140625</v>
       </c>
-      <c r="X27">
+      <c r="Z27">
         <v>1665.85998535156</v>
       </c>
-      <c r="Y27">
+      <c r="AA27">
         <v>22.251119784538801</v>
       </c>
-      <c r="Z27">
+      <c r="AB27">
         <v>1643.02213464499</v>
       </c>
-      <c r="AA27">
+      <c r="AC27">
         <v>7.34961283203143</v>
       </c>
-      <c r="AB27">
+      <c r="AD27">
         <v>15.5766381714507</v>
       </c>
-      <c r="AC27">
+      <c r="AE27">
         <v>1028.84057617188</v>
       </c>
-      <c r="AD27">
+      <c r="AF27">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE27">
+      <c r="AG27">
         <v>8.1700439453125</v>
       </c>
-      <c r="AF27">
+      <c r="AH27">
         <v>2.1381723357300999E-4</v>
       </c>
-      <c r="AG27" s="1">
+      <c r="AI27" s="1">
         <v>8.0205632709242992E-6</v>
       </c>
-      <c r="AH27">
+      <c r="AJ27">
         <v>0.11571450542171099</v>
       </c>
-      <c r="AI27">
+      <c r="AK27">
         <v>1.2555634229198E-4</v>
       </c>
-      <c r="AJ27">
+      <c r="AL27">
         <v>0.99877680120442802</v>
       </c>
-      <c r="AK27">
+      <c r="AM27">
         <v>3.2174078856306401</v>
       </c>
-      <c r="AL27">
+      <c r="AN27">
         <v>1.14647223155544E-2</v>
       </c>
-      <c r="AM27">
+      <c r="AO27">
         <v>1.31773166402595E-2</v>
       </c>
-      <c r="AN27">
+      <c r="AP27">
         <v>2.3336907282916002</v>
       </c>
-      <c r="AO27">
+      <c r="AQ27">
         <v>-5.6980627944291998E-3</v>
       </c>
-      <c r="AP27">
+      <c r="AR27">
         <v>0.27037896155427199</v>
       </c>
-      <c r="AQ27" s="1">
+      <c r="AS27" s="1">
         <v>9.0231336797727396E-6</v>
       </c>
-      <c r="AR27">
+      <c r="AT27">
         <v>3.4609784209428097E-2</v>
       </c>
-      <c r="AS27">
+      <c r="AU27">
         <v>0.115762532147738</v>
       </c>
-      <c r="AT27">
+      <c r="AV27">
         <v>4.0928235744444201E-2</v>
       </c>
-      <c r="AU27">
+      <c r="AW27">
         <v>0.11322938909739</v>
       </c>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28">
         <v>4.40074129789887</v>
       </c>
-      <c r="C28">
+      <c r="E28">
         <v>6.10135006348602</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>1659.33195800781</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <v>0.101285862504202</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1385134.10827939</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>3.5875863459393999E-4</v>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>3.6990210337399E-3</v>
       </c>
-      <c r="I28">
+      <c r="K28">
         <v>-1203.22470270589</v>
       </c>
-      <c r="J28">
+      <c r="L28">
         <v>0.97657878402672504</v>
       </c>
-      <c r="K28">
+      <c r="M28">
         <v>1.8795269350836801</v>
       </c>
-      <c r="L28">
+      <c r="N28">
         <v>4.4957946707220503E-2</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>2.00000022073734</v>
       </c>
-      <c r="N28">
+      <c r="P28">
         <v>10.1010101010101</v>
       </c>
-      <c r="O28">
+      <c r="Q28">
         <v>8.8398312512873403E-2</v>
       </c>
-      <c r="P28">
+      <c r="R28">
         <v>171.71717171717199</v>
       </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
         <v>2.9451504536260598E-2</v>
       </c>
-      <c r="S28">
+      <c r="U28">
         <v>-322.79556967773402</v>
       </c>
-      <c r="T28">
+      <c r="V28">
         <v>0.72836412035601705</v>
       </c>
-      <c r="U28">
+      <c r="W28">
         <v>0.55727860382957894</v>
       </c>
-      <c r="V28">
+      <c r="X28">
         <v>-2.81637995149119E-3</v>
       </c>
-      <c r="W28">
+      <c r="Y28">
         <v>1621.5400390625</v>
       </c>
-      <c r="X28">
+      <c r="Z28">
         <v>1659.34997558594</v>
       </c>
-      <c r="Y28">
+      <c r="AA28">
         <v>10.6785396181435</v>
       </c>
-      <c r="Z28">
+      <c r="AB28">
         <v>1637.3101243992401</v>
       </c>
-      <c r="AA28">
+      <c r="AC28">
         <v>17.428403932678101</v>
       </c>
-      <c r="AB28">
+      <c r="AD28">
         <v>9.7187816205462205</v>
       </c>
-      <c r="AC28">
+      <c r="AE28">
         <v>1029.54748535156</v>
       </c>
-      <c r="AD28">
+      <c r="AF28">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE28">
+      <c r="AG28">
         <v>9.9000244140625</v>
       </c>
-      <c r="AF28">
+      <c r="AH28">
         <v>4.0994158741396499E-3</v>
       </c>
-      <c r="AG28" s="1">
+      <c r="AI28" s="1">
         <v>-7.7500028895132394E-6</v>
       </c>
-      <c r="AH28">
+      <c r="AJ28">
         <v>0.16372061993100101</v>
       </c>
-      <c r="AI28">
+      <c r="AK28">
         <v>4.32254258002E-4</v>
       </c>
-      <c r="AJ28">
+      <c r="AL28">
         <v>0.997943886096193</v>
       </c>
-      <c r="AK28">
+      <c r="AM28">
         <v>3.2174078848929599</v>
       </c>
-      <c r="AL28">
+      <c r="AN28">
         <v>2.5121285816483201E-2</v>
       </c>
-      <c r="AM28">
+      <c r="AO28">
         <v>2.8651629832420301E-2</v>
       </c>
-      <c r="AN28">
+      <c r="AP28">
         <v>2.5858856828760302</v>
       </c>
-      <c r="AO28">
+      <c r="AQ28">
         <v>-7.8891391989522996E-2</v>
       </c>
-      <c r="AP28">
+      <c r="AR28">
         <v>7.5530010792836E-2</v>
       </c>
-      <c r="AQ28" s="1">
+      <c r="AS28" s="1">
         <v>-8.71875325063865E-6</v>
       </c>
-      <c r="AR28">
+      <c r="AT28">
         <v>4.74346059034828E-2</v>
       </c>
-      <c r="AS28">
+      <c r="AU28">
         <v>0.16382599953718699</v>
       </c>
-      <c r="AT28">
+      <c r="AV28">
         <v>5.7921237603621202E-2</v>
       </c>
-      <c r="AU28">
+      <c r="AW28">
         <v>0.14987221803797901</v>
       </c>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>73</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29">
         <v>6.8893900821578997</v>
       </c>
-      <c r="C29">
+      <c r="E29">
         <v>8.7188096473787695</v>
       </c>
-      <c r="D29">
+      <c r="F29">
         <v>633.25661621093798</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <v>0.13089074540953399</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>514693.20692035998</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>4.4707156868582001E-4</v>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>1.3967728328785199E-2</v>
       </c>
-      <c r="I29">
+      <c r="K29">
         <v>-426.61496095382699</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>0.15530142793971499</v>
       </c>
-      <c r="K29">
+      <c r="M29">
         <v>-0.48054752813873802</v>
       </c>
-      <c r="L29">
+      <c r="N29">
         <v>4.6381870274807203E-2</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>2.0000002139554298</v>
       </c>
-      <c r="N29">
+      <c r="P29">
         <v>10.1010101010101</v>
       </c>
-      <c r="O29">
+      <c r="Q29">
         <v>8.0455688869826597E-2</v>
       </c>
-      <c r="P29">
+      <c r="R29">
         <v>161.616161616162</v>
       </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
         <v>3.6685015942222503E-2</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>-116.704707929948</v>
       </c>
-      <c r="T29">
+      <c r="V29">
         <v>0.72686353043142105</v>
       </c>
-      <c r="U29">
+      <c r="W29">
         <v>0.55615614080328202</v>
       </c>
-      <c r="V29">
+      <c r="X29">
         <v>-2.3483079029073201E-3</v>
       </c>
-      <c r="W29">
+      <c r="Y29">
         <v>589.54901123046898</v>
       </c>
-      <c r="X29">
+      <c r="Z29">
         <v>633.322021484375</v>
       </c>
-      <c r="Y29">
+      <c r="AA29">
         <v>18.8573543691321</v>
       </c>
-      <c r="Z29">
+      <c r="AB29">
         <v>608.30933822391899</v>
       </c>
-      <c r="AA29">
+      <c r="AC29">
         <v>15.641869756546001</v>
       </c>
-      <c r="AB29">
+      <c r="AD29">
         <v>9.2748007854006609</v>
       </c>
-      <c r="AC29">
+      <c r="AE29">
         <v>1027.42639160156</v>
       </c>
-      <c r="AD29">
+      <c r="AF29">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE29">
+      <c r="AG29">
         <v>9.11102294921875</v>
       </c>
-      <c r="AF29">
+      <c r="AH29">
         <v>1.91467178139041E-3</v>
       </c>
-      <c r="AG29" s="1">
+      <c r="AI29" s="1">
         <v>1.0881245288709401E-6</v>
       </c>
-      <c r="AH29">
+      <c r="AJ29">
         <v>0.25202180269115199</v>
       </c>
-      <c r="AI29">
+      <c r="AK29">
         <v>6.9255633278477E-4</v>
       </c>
-      <c r="AJ29">
+      <c r="AL29">
         <v>0.99580391299932303</v>
       </c>
-      <c r="AK29">
+      <c r="AM29">
         <v>3.2174078638157799</v>
       </c>
-      <c r="AL29">
+      <c r="AN29">
         <v>3.6073738099045599E-2</v>
       </c>
-      <c r="AM29">
+      <c r="AO29">
         <v>4.1243155869639003E-2</v>
       </c>
-      <c r="AN29">
+      <c r="AP29">
         <v>4.2570954509491301</v>
       </c>
-      <c r="AO29">
+      <c r="AQ29">
         <v>-0.1039766407806</v>
       </c>
-      <c r="AP29">
+      <c r="AR29">
         <v>6.1534786623089602E-2</v>
       </c>
-      <c r="AQ29" s="1">
+      <c r="AS29" s="1">
         <v>1.22414009499032E-6</v>
       </c>
-      <c r="AR29">
+      <c r="AT29">
         <v>7.5048660545669901E-2</v>
       </c>
-      <c r="AS29">
+      <c r="AU29">
         <v>0.252126632083709</v>
       </c>
-      <c r="AT29">
+      <c r="AV29">
         <v>8.9140225632061698E-2</v>
       </c>
-      <c r="AU29">
+      <c r="AW29">
         <v>0.23174400839375101</v>
       </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>74</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30">
         <v>5.9652264121815497</v>
       </c>
-      <c r="C30">
+      <c r="E30">
         <v>7.3245554478710799</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>641.80179443359395</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <v>0.14422061711618001</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>522871.45099988102</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>5.9333852260785001E-4</v>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>1.1587378184395401E-2</v>
       </c>
-      <c r="I30">
+      <c r="K30">
         <v>-435.66387569643098</v>
       </c>
-      <c r="J30">
+      <c r="L30">
         <v>0.57496357292737099</v>
       </c>
-      <c r="K30">
+      <c r="M30">
         <v>-7.31216663359682E-2</v>
       </c>
-      <c r="L30">
+      <c r="N30">
         <v>4.8554292153580501E-2</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>2.0000003276146101</v>
       </c>
-      <c r="N30">
+      <c r="P30">
         <v>10.1010101010101</v>
       </c>
-      <c r="O30">
+      <c r="Q30">
         <v>8.6168442780652998E-2</v>
       </c>
-      <c r="P30">
+      <c r="R30">
         <v>181.81818181818201</v>
       </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
         <v>3.78201211831585E-2</v>
       </c>
-      <c r="S30">
+      <c r="U30">
         <v>-119.290090586758</v>
       </c>
-      <c r="T30">
+      <c r="V30">
         <v>0.72936459999899805</v>
       </c>
-      <c r="U30">
+      <c r="W30">
         <v>0.55735131888002198</v>
       </c>
-      <c r="V30">
+      <c r="X30">
         <v>-2.14693249946584E-3</v>
       </c>
-      <c r="W30">
+      <c r="Y30">
         <v>599.97601318359398</v>
       </c>
-      <c r="X30">
+      <c r="Z30">
         <v>641.84100341796898</v>
       </c>
-      <c r="Y30">
+      <c r="AA30">
         <v>19.680810180477899</v>
       </c>
-      <c r="Z30">
+      <c r="AB30">
         <v>618.01714294678698</v>
       </c>
-      <c r="AA30">
+      <c r="AC30">
         <v>14.963871260254001</v>
       </c>
-      <c r="AB30">
+      <c r="AD30">
         <v>7.2219599060058499</v>
       </c>
-      <c r="AC30">
+      <c r="AE30">
         <v>1030.96166992188</v>
       </c>
-      <c r="AD30">
+      <c r="AF30">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE30">
+      <c r="AG30">
         <v>9.72601318359375</v>
       </c>
-      <c r="AF30">
+      <c r="AH30">
         <v>3.4599964397232999E-4</v>
       </c>
-      <c r="AG30" s="1">
+      <c r="AI30" s="1">
         <v>8.0723822840688008E-6</v>
       </c>
-      <c r="AH30">
+      <c r="AJ30">
         <v>0.25822632788468403</v>
       </c>
-      <c r="AI30">
+      <c r="AK30">
         <v>1.0273462452372901E-3</v>
       </c>
-      <c r="AJ30">
+      <c r="AL30">
         <v>0.99524395797257803</v>
       </c>
-      <c r="AK30">
+      <c r="AM30">
         <v>3.21740786177295</v>
       </c>
-      <c r="AL30">
+      <c r="AN30">
         <v>3.8005608021449602E-2</v>
       </c>
-      <c r="AM30">
+      <c r="AO30">
         <v>4.3884771513774103E-2</v>
       </c>
-      <c r="AN30">
+      <c r="AP30">
         <v>4.25834310429269</v>
       </c>
-      <c r="AO30">
+      <c r="AQ30">
         <v>3.60766607486425E-3</v>
       </c>
-      <c r="AP30">
+      <c r="AR30">
         <v>9.41081335282382E-2</v>
       </c>
-      <c r="AQ30" s="1">
+      <c r="AS30" s="1">
         <v>9.0814300696026907E-6</v>
       </c>
-      <c r="AR30">
+      <c r="AT30">
         <v>7.6572841309408196E-2</v>
       </c>
-      <c r="AS30">
+      <c r="AU30">
         <v>0.25837290016664899</v>
       </c>
-      <c r="AT30">
+      <c r="AV30">
         <v>9.1348614891323995E-2</v>
       </c>
-      <c r="AU30">
+      <c r="AW30">
         <v>0.234993551456285</v>
       </c>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>75</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31">
         <v>6.0548482551165499</v>
       </c>
-      <c r="C31">
+      <c r="E31">
         <v>7.4402499231472703</v>
       </c>
-      <c r="D31">
+      <c r="F31">
         <v>636.84859619140605</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <v>0.14739275445653399</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>517078.67487273802</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>4.8377060609337998E-4</v>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>1.1923133401772101E-2</v>
       </c>
-      <c r="I31">
+      <c r="K31">
         <v>-429.49237534227501</v>
       </c>
-      <c r="J31">
+      <c r="L31">
         <v>0.138237705343742</v>
       </c>
-      <c r="K31">
+      <c r="M31">
         <v>-0.36034578619510299</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>4.7592580682537397E-2</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>2.0000002599202702</v>
       </c>
-      <c r="N31">
+      <c r="P31">
         <v>10.1010101010101</v>
       </c>
-      <c r="O31">
+      <c r="Q31">
         <v>8.4018412279443497E-2</v>
       </c>
-      <c r="P31">
+      <c r="R31">
         <v>181.81818181818201</v>
       </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
         <v>3.2323345367241303E-2</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>-116.96799633779899</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>0.72836412035601705</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>0.55677857990788204</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>-2.1015825750647101E-3</v>
       </c>
-      <c r="W31">
+      <c r="Y31">
         <v>589.65399169921898</v>
       </c>
-      <c r="X31">
+      <c r="Z31">
         <v>637.03997802734398</v>
       </c>
-      <c r="Y31">
+      <c r="AA31">
         <v>20.304999753503999</v>
       </c>
-      <c r="Z31">
+      <c r="AB31">
         <v>611.17721643421203</v>
       </c>
-      <c r="AA31">
+      <c r="AC31">
         <v>15.869887982116699</v>
       </c>
-      <c r="AB31">
+      <c r="AD31">
         <v>11.2119483894044</v>
       </c>
-      <c r="AC31">
+      <c r="AE31">
         <v>1029.54748535156</v>
       </c>
-      <c r="AD31">
+      <c r="AF31">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE31">
+      <c r="AG31">
         <v>13.02197265625</v>
       </c>
-      <c r="AF31">
+      <c r="AH31">
         <v>9.8365785853093989E-4</v>
       </c>
-      <c r="AG31" s="1">
+      <c r="AI31" s="1">
         <v>-1.33608724735647E-6</v>
       </c>
-      <c r="AH31">
+      <c r="AJ31">
         <v>0.27151041214022298</v>
       </c>
-      <c r="AI31">
+      <c r="AK31">
         <v>1.12155617957945E-3</v>
       </c>
-      <c r="AJ31">
+      <c r="AL31">
         <v>0.99501720133099603</v>
       </c>
-      <c r="AK31">
+      <c r="AM31">
         <v>3.21740786021306</v>
       </c>
-      <c r="AL31">
+      <c r="AN31">
         <v>3.9821915181720298E-2</v>
       </c>
-      <c r="AM31">
+      <c r="AO31">
         <v>4.5903846465922701E-2</v>
       </c>
-      <c r="AN31">
+      <c r="AP31">
         <v>4.4494731469601003</v>
       </c>
-      <c r="AO31">
+      <c r="AQ31">
         <v>1.7079150990567199E-2</v>
       </c>
-      <c r="AP31">
+      <c r="AR31">
         <v>7.1548811273973903E-2</v>
       </c>
-      <c r="AQ31" s="1">
+      <c r="AS31" s="1">
         <v>-1.5030981532914399E-6</v>
       </c>
-      <c r="AR31">
+      <c r="AT31">
         <v>8.0686101149452794E-2</v>
       </c>
-      <c r="AS31">
+      <c r="AU31">
         <v>0.27168211402301201</v>
       </c>
-      <c r="AT31">
+      <c r="AV31">
         <v>9.6054132576380097E-2</v>
       </c>
-      <c r="AU31">
+      <c r="AW31">
         <v>0.24558817236422201</v>
       </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>76</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32">
         <v>5.8020790288227504</v>
       </c>
-      <c r="C32">
+      <c r="E32">
         <v>7.2502384470194698</v>
       </c>
-      <c r="D32">
+      <c r="F32">
         <v>612.826586914063</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <v>0.122685145140808</v>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>499905.119495905</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>4.8379739345034002E-4</v>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>1.2015263640605799E-2</v>
       </c>
-      <c r="I32">
+      <c r="K32">
         <v>-417.78482038092801</v>
       </c>
-      <c r="J32">
+      <c r="L32">
         <v>0.279053665244129</v>
       </c>
-      <c r="K32">
+      <c r="M32">
         <v>-6.0367956508827099E-2</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>5.0557294655331701E-2</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>2.0000002457627399</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>10.1010101010101</v>
       </c>
-      <c r="O32">
+      <c r="Q32">
         <v>8.8246537164114597E-2</v>
       </c>
-      <c r="P32">
+      <c r="R32">
         <v>191.919191919192</v>
       </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
         <v>4.2509465480961399E-2</v>
       </c>
-      <c r="S32">
+      <c r="U32">
         <v>-113.520394295404</v>
       </c>
-      <c r="T32">
+      <c r="V32">
         <v>0.72736364071303605</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>0.55675383779154897</v>
       </c>
-      <c r="V32">
+      <c r="X32">
         <v>-2.3098877719980198E-3</v>
       </c>
-      <c r="W32">
+      <c r="Y32">
         <v>573.45397949218795</v>
       </c>
-      <c r="X32">
+      <c r="Z32">
         <v>612.89398193359398</v>
       </c>
-      <c r="Y32">
+      <c r="AA32">
         <v>19.616846723243398</v>
       </c>
-      <c r="Z32">
+      <c r="AB32">
         <v>590.84567416066704</v>
       </c>
-      <c r="AA32">
+      <c r="AC32">
         <v>12.6288485295411</v>
       </c>
-      <c r="AB32">
+      <c r="AD32">
         <v>7.1949333020020303</v>
       </c>
-      <c r="AC32">
+      <c r="AE32">
         <v>1028.13330078125</v>
       </c>
-      <c r="AD32">
+      <c r="AF32">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE32">
+      <c r="AG32">
         <v>9.4749755859375</v>
       </c>
-      <c r="AF32">
+      <c r="AH32">
         <v>1.16070727243134E-3</v>
       </c>
-      <c r="AG32" s="1">
+      <c r="AI32" s="1">
         <v>-4.3249450035398003E-6</v>
       </c>
-      <c r="AH32">
+      <c r="AJ32">
         <v>0.23393833188289201</v>
       </c>
-      <c r="AI32">
+      <c r="AK32">
         <v>8.1685359159707003E-4</v>
       </c>
-      <c r="AJ32">
+      <c r="AL32">
         <v>0.99674029205952297</v>
       </c>
-      <c r="AK32">
+      <c r="AM32">
         <v>3.2174078686140701</v>
       </c>
-      <c r="AL32">
+      <c r="AN32">
         <v>3.6404864674028599E-2</v>
       </c>
-      <c r="AM32">
+      <c r="AO32">
         <v>4.23109592200792E-2</v>
       </c>
-      <c r="AN32">
+      <c r="AP32">
         <v>3.69707987744393</v>
       </c>
-      <c r="AO32">
+      <c r="AQ32">
         <v>-6.6268874204526707E-2</v>
       </c>
-      <c r="AP32">
+      <c r="AR32">
         <v>0.11905349951944499</v>
       </c>
-      <c r="AQ32" s="1">
+      <c r="AS32" s="1">
         <v>-4.8655631289809697E-6</v>
       </c>
-      <c r="AR32">
+      <c r="AT32">
         <v>6.9259557833021707E-2</v>
       </c>
-      <c r="AS32">
+      <c r="AU32">
         <v>0.234062123806627</v>
       </c>
-      <c r="AT32">
+      <c r="AV32">
         <v>8.2753457481292994E-2</v>
       </c>
-      <c r="AU32">
+      <c r="AW32">
         <v>0.208264918832267</v>
       </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>77</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33">
         <v>6.7635826758735904</v>
       </c>
-      <c r="C33">
+      <c r="E33">
         <v>8.7200130731048109</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>626.35640869140605</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <v>0.12968756937798201</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>507466.42115166801</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>4.2929633186483001E-4</v>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>1.41050775376388E-2</v>
       </c>
-      <c r="I33">
+      <c r="K33">
         <v>-418.174537847002</v>
       </c>
-      <c r="J33">
+      <c r="L33">
         <v>0.76911196914715696</v>
       </c>
-      <c r="K33">
+      <c r="M33">
         <v>0.16302040012550501</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>5.3932418935831103E-2</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>2.0000001849831102</v>
       </c>
-      <c r="N33">
+      <c r="P33">
         <v>10.1010101010101</v>
       </c>
-      <c r="O33">
+      <c r="Q33">
         <v>8.56365331806902E-2</v>
       </c>
-      <c r="P33">
+      <c r="R33">
         <v>181.81818181818201</v>
       </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
         <v>4.07822783795471E-2</v>
       </c>
-      <c r="S33">
+      <c r="U33">
         <v>-115.516314585404</v>
       </c>
-      <c r="T33">
+      <c r="V33">
         <v>0.72886457607730104</v>
       </c>
-      <c r="U33">
+      <c r="W33">
         <v>0.557508450749716</v>
       </c>
-      <c r="V33">
+      <c r="X33">
         <v>-2.1271612776771298E-3</v>
       </c>
-      <c r="W33">
+      <c r="Y33">
         <v>582.12902832031205</v>
       </c>
-      <c r="X33">
+      <c r="Z33">
         <v>626.38800048828102</v>
       </c>
-      <c r="Y33">
+      <c r="AA33">
         <v>18.378680880416798</v>
       </c>
-      <c r="Z33">
+      <c r="AB33">
         <v>599.77152309657799</v>
       </c>
-      <c r="AA33">
+      <c r="AC33">
         <v>18.6208085256347</v>
       </c>
-      <c r="AB33">
+      <c r="AD33">
         <v>7.2598435527343099</v>
       </c>
-      <c r="AC33">
+      <c r="AE33">
         <v>1030.2548828125</v>
       </c>
-      <c r="AD33">
+      <c r="AF33">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE33">
+      <c r="AG33">
         <v>8.16998291015625</v>
       </c>
-      <c r="AF33">
+      <c r="AH33">
         <v>1.44118276739893E-3</v>
       </c>
-      <c r="AG33" s="1">
+      <c r="AI33" s="1">
         <v>-7.0004610712124596E-6</v>
       </c>
-      <c r="AH33">
+      <c r="AJ33">
         <v>0.239676444194029</v>
       </c>
-      <c r="AI33">
+      <c r="AK33">
         <v>7.8118142775793003E-4</v>
       </c>
-      <c r="AJ33">
+      <c r="AL33">
         <v>0.99642847638517196</v>
       </c>
-      <c r="AK33">
+      <c r="AM33">
         <v>3.2174078668155102</v>
       </c>
-      <c r="AL33">
+      <c r="AN33">
         <v>3.7346867695867203E-2</v>
       </c>
-      <c r="AM33">
+      <c r="AO33">
         <v>4.2820679156897003E-2</v>
       </c>
-      <c r="AN33">
+      <c r="AP33">
         <v>3.7927469939203702</v>
       </c>
-      <c r="AO33">
+      <c r="AQ33">
         <v>-7.4059230303762894E-2</v>
       </c>
-      <c r="AP33">
+      <c r="AR33">
         <v>0.12657107809538201</v>
       </c>
-      <c r="AQ33" s="1">
+      <c r="AS33" s="1">
         <v>-7.8755187051044E-6</v>
       </c>
-      <c r="AR33">
+      <c r="AT33">
         <v>7.1153765368671198E-2</v>
       </c>
-      <c r="AS33">
+      <c r="AU33">
         <v>0.23977838859542899</v>
       </c>
-      <c r="AT33">
+      <c r="AV33">
         <v>8.4774462278908405E-2</v>
       </c>
-      <c r="AU33">
+      <c r="AW33">
         <v>0.21604071813297501</v>
       </c>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34">
         <v>7.0722112206171497</v>
       </c>
-      <c r="C34">
+      <c r="E34">
         <v>8.4806691208305498</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>626.145593261719</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <v>0.142530213462707</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>508161.065428806</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>5.0443641243265002E-4</v>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>1.38052619072526E-2</v>
       </c>
-      <c r="I34">
+      <c r="K34">
         <v>-423.92813206002398</v>
       </c>
-      <c r="J34">
+      <c r="L34">
         <v>0.36443141763273701</v>
       </c>
-      <c r="K34">
+      <c r="M34">
         <v>-0.43345348213896001</v>
       </c>
-      <c r="L34">
+      <c r="N34">
         <v>4.7462450584972303E-2</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>2.0000002386369</v>
       </c>
-      <c r="N34">
+      <c r="P34">
         <v>10.1010101010101</v>
       </c>
-      <c r="O34">
+      <c r="Q34">
         <v>8.3160846460704305E-2</v>
       </c>
-      <c r="P34">
+      <c r="R34">
         <v>161.616161616162</v>
       </c>
-      <c r="Q34">
+      <c r="S34">
         <v>90</v>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>3.8548951730593299E-2</v>
       </c>
-      <c r="S34">
+      <c r="U34">
         <v>-115.78612339927101</v>
       </c>
-      <c r="T34">
+      <c r="V34">
         <v>0.72686353043142105</v>
       </c>
-      <c r="U34">
+      <c r="W34">
         <v>0.55648050865300502</v>
       </c>
-      <c r="V34">
+      <c r="X34">
         <v>-2.33511412115595E-3</v>
       </c>
-      <c r="W34">
+      <c r="Y34">
         <v>583.58502197265602</v>
       </c>
-      <c r="X34">
+      <c r="Z34">
         <v>628.45697021484398</v>
       </c>
-      <c r="Y34">
+      <c r="AA34">
         <v>26.733055682890999</v>
       </c>
-      <c r="Z34">
+      <c r="AB34">
         <v>600.600914851487</v>
       </c>
-      <c r="AA34">
+      <c r="AC34">
         <v>14.8118906311036</v>
       </c>
-      <c r="AB34">
+      <c r="AD34">
         <v>3.3280006840665202</v>
       </c>
-      <c r="AC34">
+      <c r="AE34">
         <v>1027.42639160156</v>
       </c>
-      <c r="AD34">
+      <c r="AF34">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE34">
+      <c r="AG34">
         <v>14.1499633789062</v>
       </c>
-      <c r="AF34">
+      <c r="AH34">
         <v>1.50635340714421E-3</v>
       </c>
-      <c r="AG34" s="1">
+      <c r="AI34" s="1">
         <v>2.3001641631299202E-6</v>
       </c>
-      <c r="AH34">
+      <c r="AJ34">
         <v>0.27255112775787599</v>
       </c>
-      <c r="AI34">
+      <c r="AK34">
         <v>9.0929676818537E-4</v>
       </c>
-      <c r="AJ34">
+      <c r="AL34">
         <v>0.995297998120663</v>
       </c>
-      <c r="AK34">
+      <c r="AM34">
         <v>3.2174078603599998</v>
       </c>
-      <c r="AL34">
+      <c r="AN34">
         <v>4.0507486816207298E-2</v>
       </c>
-      <c r="AM34">
+      <c r="AO34">
         <v>4.6449199179379799E-2</v>
       </c>
-      <c r="AN34">
+      <c r="AP34">
         <v>4.4689762626163896</v>
       </c>
-      <c r="AO34">
+      <c r="AQ34">
         <v>9.3227929617055103E-2</v>
       </c>
-      <c r="AP34">
+      <c r="AR34">
         <v>7.1589020432001702E-2</v>
       </c>
-      <c r="AQ34" s="1">
+      <c r="AS34" s="1">
         <v>2.5876846835378598E-6</v>
       </c>
-      <c r="AR34">
+      <c r="AT34">
         <v>8.1118031596926196E-2</v>
       </c>
-      <c r="AS34">
+      <c r="AU34">
         <v>0.272710772005121</v>
       </c>
-      <c r="AT34">
+      <c r="AV34">
         <v>9.6417818093722601E-2</v>
       </c>
-      <c r="AU34">
+      <c r="AW34">
         <v>0.24743124735716801</v>
       </c>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35">
         <v>4.9546735475655002</v>
       </c>
-      <c r="C35">
+      <c r="E35">
         <v>6.0680273404810503</v>
       </c>
-      <c r="D35">
+      <c r="F35">
         <v>596.00780029296902</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <v>0.128924779488896</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>488660.23262184497</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>6.4304574098490003E-4</v>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>1.03357525582129E-2</v>
       </c>
-      <c r="I35">
+      <c r="K35">
         <v>-410.99209334808103</v>
       </c>
-      <c r="J35">
+      <c r="L35">
         <v>-0.25788507758953499</v>
       </c>
-      <c r="K35">
+      <c r="M35">
         <v>-0.569294972987899</v>
       </c>
-      <c r="L35">
+      <c r="N35">
         <v>3.9628618711556901E-2</v>
       </c>
-      <c r="M35">
+      <c r="O35">
         <v>2.0000004398548898</v>
       </c>
-      <c r="N35">
+      <c r="P35">
         <v>10.1010101010101</v>
       </c>
-      <c r="O35">
+      <c r="Q35">
         <v>7.2299654351691001E-2</v>
       </c>
-      <c r="P35">
+      <c r="R35">
         <v>161.616161616162</v>
       </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
         <v>3.7394721064175497E-2</v>
       </c>
-      <c r="S35">
+      <c r="U35">
         <v>-111.03440674765601</v>
       </c>
-      <c r="T35">
+      <c r="V35">
         <v>0.72986505572028204</v>
       </c>
-      <c r="U35">
+      <c r="W35">
         <v>0.55775349701531496</v>
       </c>
-      <c r="V35">
+      <c r="X35">
         <v>-2.79224054720695E-3</v>
       </c>
-      <c r="W35">
+      <c r="Y35">
         <v>560.3330078125</v>
       </c>
-      <c r="X35">
+      <c r="Z35">
         <v>596.28399658203102</v>
       </c>
-      <c r="Y35">
+      <c r="AA35">
         <v>14.961653374601999</v>
       </c>
-      <c r="Z35">
+      <c r="AB35">
         <v>577.58502991973705</v>
       </c>
-      <c r="AA35">
+      <c r="AC35">
         <v>10.584931686614899</v>
       </c>
-      <c r="AB35">
+      <c r="AD35">
         <v>10.405835556136999</v>
       </c>
-      <c r="AC35">
+      <c r="AE35">
         <v>1031.66906738281</v>
       </c>
-      <c r="AD35">
+      <c r="AF35">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE35">
+      <c r="AG35">
         <v>9.1929931640625</v>
       </c>
-      <c r="AF35">
+      <c r="AH35">
         <v>1.4781768908355699E-3</v>
       </c>
-      <c r="AG35" s="1">
+      <c r="AI35" s="1">
         <v>1.43056355393518E-6</v>
       </c>
-      <c r="AH35">
+      <c r="AJ35">
         <v>0.25043212809377202</v>
       </c>
-      <c r="AI35">
+      <c r="AK35">
         <v>7.1964648956071001E-4</v>
       </c>
-      <c r="AJ35">
+      <c r="AL35">
         <v>0.99576701532948897</v>
       </c>
-      <c r="AK35">
+      <c r="AM35">
         <v>3.2174078613913899</v>
       </c>
-      <c r="AL35">
+      <c r="AN35">
         <v>3.43468761472581E-2</v>
       </c>
-      <c r="AM35">
+      <c r="AO35">
         <v>3.9444017479422999E-2</v>
       </c>
-      <c r="AN35">
+      <c r="AP35">
         <v>4.3105442260435796</v>
       </c>
-      <c r="AO35">
+      <c r="AQ35">
         <v>-3.6111087759931403E-2</v>
       </c>
-      <c r="AP35">
+      <c r="AR35">
         <v>6.6902788889665707E-2</v>
       </c>
-      <c r="AQ35" s="1">
+      <c r="AS35" s="1">
         <v>1.6093839982120401E-6</v>
       </c>
-      <c r="AR35">
+      <c r="AT35">
         <v>7.4768221264456605E-2</v>
       </c>
-      <c r="AS35">
+      <c r="AU35">
         <v>0.25053601670247999</v>
       </c>
-      <c r="AT35">
+      <c r="AV35">
         <v>8.8577858170891505E-2</v>
       </c>
-      <c r="AU35">
+      <c r="AW35">
         <v>0.23107524009892699</v>
       </c>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>80</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36">
         <v>5.1879511671638898</v>
       </c>
-      <c r="C36">
+      <c r="E36">
         <v>6.63754841194711</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>602.17698974609402</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <v>0.11985332603071</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>494101.85756874498</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>5.0586591918479001E-4</v>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>1.11793495291797E-2</v>
       </c>
-      <c r="I36">
+      <c r="K36">
         <v>-414.31211685050403</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-0.54502720117745196</v>
       </c>
-      <c r="K36">
+      <c r="M36">
         <v>-0.209752973005846</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>4.7031269511694299E-2</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>2.0000002440631999</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>10.1010101010101</v>
       </c>
-      <c r="O36">
+      <c r="Q36">
         <v>7.96643426882091E-2</v>
       </c>
-      <c r="P36">
+      <c r="R36">
         <v>141.414141414141</v>
       </c>
-      <c r="Q36">
+      <c r="S36">
         <v>90</v>
       </c>
-      <c r="R36">
+      <c r="T36">
         <v>3.8225823009330202E-2</v>
       </c>
-      <c r="S36">
+      <c r="U36">
         <v>-111.496846374505</v>
       </c>
-      <c r="T36">
+      <c r="V36">
         <v>0.72636307471013695</v>
       </c>
-      <c r="U36">
+      <c r="W36">
         <v>0.55585910586741405</v>
       </c>
-      <c r="V36">
+      <c r="X36">
         <v>-2.4725570232314001E-3</v>
       </c>
-      <c r="W36">
+      <c r="Y36">
         <v>564.57897949218795</v>
       </c>
-      <c r="X36">
+      <c r="Z36">
         <v>602.25897216796898</v>
       </c>
-      <c r="Y36">
+      <c r="AA36">
         <v>12.8540716410009</v>
       </c>
-      <c r="Z36">
+      <c r="AB36">
         <v>583.99505788966201</v>
       </c>
-      <c r="AA36">
+      <c r="AC36">
         <v>10.818862861084099</v>
       </c>
-      <c r="AB36">
+      <c r="AD36">
         <v>14.0078057770997</v>
       </c>
-      <c r="AC36">
+      <c r="AE36">
         <v>1026.71899414062</v>
       </c>
-      <c r="AD36">
+      <c r="AF36">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE36">
+      <c r="AG36">
         <v>8.5260009765625</v>
       </c>
-      <c r="AF36">
+      <c r="AH36">
         <v>1.5857564089038099E-3</v>
       </c>
-      <c r="AG36" s="1">
+      <c r="AI36" s="1">
         <v>1.37021478067006E-7</v>
       </c>
-      <c r="AH36">
+      <c r="AJ36">
         <v>0.22935712950586901</v>
       </c>
-      <c r="AI36">
+      <c r="AK36">
         <v>5.9508084122047999E-4</v>
       </c>
-      <c r="AJ36">
+      <c r="AL36">
         <v>0.99652938687754</v>
       </c>
-      <c r="AK36">
+      <c r="AM36">
         <v>3.21740706157656</v>
       </c>
-      <c r="AL36">
+      <c r="AN36">
         <v>3.3179633987641399E-2</v>
       </c>
-      <c r="AM36">
+      <c r="AO36">
         <v>3.79381317311E-2</v>
       </c>
-      <c r="AN36">
+      <c r="AP36">
         <v>3.84468303811573</v>
       </c>
-      <c r="AO36">
+      <c r="AQ36">
         <v>3.68395706961199E-2</v>
       </c>
-      <c r="AP36">
+      <c r="AR36">
         <v>8.8559768899041894E-2</v>
       </c>
-      <c r="AQ36" s="1">
+      <c r="AS36" s="1">
         <v>1.5414916285330199E-7</v>
       </c>
-      <c r="AR36">
+      <c r="AT36">
         <v>6.8371887876781307E-2</v>
       </c>
-      <c r="AS36">
+      <c r="AU36">
         <v>0.22946369153828799</v>
       </c>
-      <c r="AT36">
+      <c r="AV36">
         <v>8.1127666161410594E-2</v>
       </c>
-      <c r="AU36">
+      <c r="AW36">
         <v>0.21026334514398401</v>
       </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>81</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37">
         <v>6.2460925915314798</v>
       </c>
-      <c r="C37">
+      <c r="E37">
         <v>7.14265640904829</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>598.61040039062505</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <v>0.13576506719816001</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>492424.83403973997</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>9.1469878212188996E-4</v>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>1.20562564124755E-2</v>
       </c>
-      <c r="I37">
+      <c r="K37">
         <v>-414.88124618552098</v>
       </c>
-      <c r="J37">
+      <c r="L37">
         <v>-0.10874133915541399</v>
       </c>
-      <c r="K37">
+      <c r="M37">
         <v>-1.2014234545861899</v>
       </c>
-      <c r="L37">
+      <c r="N37">
         <v>4.1425164808517302E-2</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>2.00000062023947</v>
       </c>
-      <c r="N37">
+      <c r="P37">
         <v>10.1010101010101</v>
       </c>
-      <c r="O37">
+      <c r="Q37">
         <v>8.4936934527812494E-2</v>
       </c>
-      <c r="P37">
+      <c r="R37">
         <v>141.414141414141</v>
       </c>
-      <c r="Q37">
+      <c r="S37">
         <v>90</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>3.5886781018746997E-2</v>
       </c>
-      <c r="S37">
+      <c r="U37">
         <v>-112.523454043659</v>
       </c>
-      <c r="T37">
+      <c r="V37">
         <v>0.72886457607730104</v>
       </c>
-      <c r="U37">
+      <c r="W37">
         <v>0.55727860382957894</v>
       </c>
-      <c r="V37">
+      <c r="X37">
         <v>-2.9290457405615699E-3</v>
       </c>
-      <c r="W37">
+      <c r="Y37">
         <v>566.96002197265602</v>
       </c>
-      <c r="X37">
+      <c r="Z37">
         <v>598.70202636718795</v>
       </c>
-      <c r="Y37">
+      <c r="AA37">
         <v>19.432476164617398</v>
       </c>
-      <c r="Z37">
+      <c r="AB37">
         <v>582.02851647287196</v>
       </c>
-      <c r="AA37">
+      <c r="AC37">
         <v>5.6839865112304997</v>
       </c>
-      <c r="AB37">
+      <c r="AD37">
         <v>6.6267928601078001</v>
       </c>
-      <c r="AC37">
+      <c r="AE37">
         <v>1030.2548828125</v>
       </c>
-      <c r="AD37">
+      <c r="AF37">
         <v>1413.50659179688</v>
       </c>
-      <c r="AE37">
+      <c r="AG37">
         <v>6.258056640625</v>
       </c>
-      <c r="AF37">
+      <c r="AH37">
         <v>1.5375507940794499E-3</v>
       </c>
-      <c r="AG37" s="1">
+      <c r="AI37" s="1">
         <v>-5.90718063291244E-6</v>
       </c>
-      <c r="AH37">
+      <c r="AJ37">
         <v>0.24967969972751</v>
       </c>
-      <c r="AI37">
+      <c r="AK37">
         <v>7.6187900674636998E-4</v>
       </c>
-      <c r="AJ37">
+      <c r="AL37">
         <v>0.99498200492756705</v>
       </c>
-      <c r="AK37">
+      <c r="AM37">
         <v>3.2174078567614899</v>
       </c>
-      <c r="AL37">
+      <c r="AN37">
         <v>3.2242514067808599E-2</v>
       </c>
-      <c r="AM37">
+      <c r="AO37">
         <v>3.6562625413633497E-2</v>
       </c>
-      <c r="AN37">
+      <c r="AP37">
         <v>4.4086380497982098</v>
       </c>
-      <c r="AO37">
+      <c r="AQ37">
         <v>-7.8109909721651299E-2</v>
       </c>
-      <c r="AP37">
+      <c r="AR37">
         <v>5.1833116531316302E-2</v>
       </c>
-      <c r="AQ37" s="1">
+      <c r="AS37" s="1">
         <v>-6.6455782120177001E-6</v>
       </c>
-      <c r="AR37">
+      <c r="AT37">
         <v>7.4711855560544799E-2</v>
       </c>
-      <c r="AS37">
+      <c r="AU37">
         <v>0.24983020767546199</v>
       </c>
-      <c r="AT37">
+      <c r="AV37">
         <v>8.8328316996255707E-2</v>
       </c>
-      <c r="AU37">
+      <c r="AW37">
         <v>0.232915212928124</v>
       </c>
     </row>
@@ -6449,7 +6597,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="1" id="{4248226E-8068-4975-85FD-4B92DE21E3FA}">
-            <xm:f>Flags!B2 = 1</xm:f>
+            <xm:f>Flags!D2 = 1</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6458,7 +6606,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B2:AU37</xm:sqref>
+          <xm:sqref>D2:AW37</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/sandbox/results/all_metrics_with_outliers_highlighted.xlsx
+++ b/sandbox/results/all_metrics_with_outliers_highlighted.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kyla Dahlin\Documents\GitHub\geodiversity_2025\sandbox\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hallerdi\Documents\Dillon_Classes\geodiversity_2025\sandbox\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F805990-278E-466B-8F6E-1EE098FAAF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82635CBB-B36C-4B24-A29D-332053FA2C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{855828C5-6364-4546-8C58-E286A8F33250}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{855828C5-6364-4546-8C58-E286A8F33250}"/>
   </bookViews>
   <sheets>
     <sheet name="all_metrics_transposed" sheetId="1" r:id="rId1"/>
